--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6501</v>
+        <v>7090</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3870</v>
+        <v>4135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>205981</v>
+        <v>305384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30278</v>
+        <v>26790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3914</v>
+        <v>4179</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1142</v>
+        <v>1057</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>413</v>
+        <v>465</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>22276</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>20663</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6089,11 +6089,11 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6123,11 +6123,11 @@
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>9347</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>25483</v>
+        <v>0</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12957,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14181,7 +14181,7 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15099,11 +15099,11 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>25022</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,7 +17241,7 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0</v>
+        <v>26312</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>0</v>
+        <v>9414</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,11 +19077,11 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,7 +19383,7 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21831,11 +21831,11 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21899,11 +21899,11 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21933,11 +21933,11 @@
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22137,7 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>536</v>
+        <v>0</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22749,7 +22749,7 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>11063</v>
+        <v>0</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>1184</v>
+        <v>0</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>30616</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24313,11 +24313,11 @@
         <v>1</v>
       </c>
       <c r="G694" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24347,11 +24347,11 @@
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24381,11 +24381,11 @@
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26285,11 +26285,11 @@
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26319,11 +26319,11 @@
         <v>1</v>
       </c>
       <c r="G753" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
@@ -26455,11 +26455,11 @@
         <v>1</v>
       </c>
       <c r="G757" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26489,11 +26489,11 @@
         <v>1</v>
       </c>
       <c r="G758" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26523,11 +26523,11 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>26935</v>
+        <v>0</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27033,7 +27033,7 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
@@ -27133,11 +27133,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6501</v>
+        <v>7090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>06cb838b496a29358957482b0a1175e7b736ed79996e6e714f6d056fd2c67b3e</t>
+          <t>4a40b19c73859fa2889a4fdb2a052ac494b009ed4b4356c6d7a5ee425c548785</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -27163,11 +27163,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3870</v>
+        <v>4135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60f10351a37044f81fb358192a9ea21a6c50f7cf595d724f4ce1e1f991bd78e7</t>
+          <t>baac4b25565154463d52191c994e991c3e2630cb7a1f0302ce1f47ab453af0b3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -27193,11 +27193,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>205981</v>
+        <v>305384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>e08244e149d9b9c6198be5039aea44be3a318a9d73c0b8a59841350d7161ac95</t>
+          <t>f980f5a9adcb02ee26ef894e758b79d724805f432cc55d1fccceca043362818f</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -27223,11 +27223,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30278</v>
+        <v>26790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3c70456527635006f984d469b7284338274e1a68c8ac56c4479ca5fcf3a6fcf4</t>
+          <t>66c2fbf183b95ad24c2dad91b1c79845163c5d3396c2d14f5fc89ee2f0bc0a4b</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -27253,11 +27253,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3914</v>
+        <v>4179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bc584d397582296a43a849fc7d71a4c11d739067ce5708fe21745c6c6ef64e1e</t>
+          <t>22b2e15e62e8fde2fa6b768133290fda57d7fb6a8c99c072b899111cba891cdc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -27283,11 +27283,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>322</v>
+        <v>553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16730aa60a56cfe04717d8702f5eb3ddfcf2a2c0378faf85ad7a6e86e8c5a048</t>
+          <t>ca4f99db1fa4a73691203b2e8a57cb4aaa1bdc19f1404c09924712c99b907c2f</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -27313,11 +27313,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>197a552266f54ccdbefa33ae8d0bb7039be41e81edfe2a9fd644c7cb54f1afe7</t>
+          <t>1ff174be837f8878dfcef1d46b4f3e51e2e0fb1a9f423cfd12419c2b4eaa6a14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -27343,11 +27343,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1142</v>
+        <v>1057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>80a1f592d1095607b0c96c4a807d6927187b7c564f58a63c26ca6e847d562cdd</t>
+          <t>c241d4054f292e054818c361342b110d8dd6e67649116ef1e393b27099b167b7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -27373,11 +27373,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>413</v>
+        <v>465</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>835e20cbea415f20d8f21444307502ac8cd9ba472682adcf71374da8fd20f4d9</t>
+          <t>cbc769266474375423e61a7127010f502c471baf5b1f616ff072d74438b7a242</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7814</v>
+        <v>5804</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5297</v>
+        <v>4057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>343457</v>
+        <v>257553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32894</v>
+        <v>24025</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3981</v>
+        <v>3774</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>539</v>
+        <v>466</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>330</v>
+        <v>154</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1150</v>
+        <v>1004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,11 +1839,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>22276</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>28324</v>
+        <v>0</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>9347</v>
+        <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>22532</v>
+        <v>0</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14283,11 +14283,11 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14351,11 +14351,11 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14385,11 +14385,11 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14453,11 +14453,11 @@
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15405,7 +15405,7 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>1116</v>
+        <v>0</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>25022</v>
+        <v>0</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>982</v>
+        <v>0</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
@@ -17921,11 +17921,11 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17955,11 +17955,11 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21831,11 +21831,11 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21899,11 +21899,11 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21933,11 +21933,11 @@
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>1016</v>
+        <v>0</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22783,11 +22783,11 @@
         <v>1</v>
       </c>
       <c r="G649" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23055,7 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>1184</v>
+        <v>0</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>30616</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,7 +24279,7 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>617</v>
+        <v>0</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27339,7 +27339,7 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -27373,11 +27373,11 @@
         <v>1</v>
       </c>
       <c r="G784" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27407,11 +27407,11 @@
         <v>1</v>
       </c>
       <c r="G785" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27441,11 +27441,11 @@
         <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27509,11 +27509,11 @@
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27543,11 +27543,11 @@
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27679,11 +27679,11 @@
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27713,11 +27713,11 @@
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27747,11 +27747,11 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27815,11 +27815,11 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>811</v>
+        <v>0</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
@@ -28121,11 +28121,11 @@
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>0</v>
+        <v>1301</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28155,11 +28155,11 @@
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28223,11 +28223,11 @@
         <v>1</v>
       </c>
       <c r="G809" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28257,11 +28257,11 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28357,11 +28357,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7814</v>
+        <v>5804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>a7fc05e6d4bbbba0318dccd1146466157e2d5a08e0f16a8bc38946487fecdf43</t>
+          <t>8a243026ded0808b79609696da8c77b8eccfd6e0d4e2909bd9891f6051f0003d</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -28387,11 +28387,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5297</v>
+        <v>4057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>b1b63ddffe7e8c4b72d71283d3b8ce7f2e5882c0d9e976c06f8fca026ef17b66</t>
+          <t>41c05245d83fb76b41c66ff123e2f51a1718bd738d9cb73750637cbb644f1c04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -28417,11 +28417,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>343457</v>
+        <v>257553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>b47de5a8d13afdf3c7f179513d5a1da5e8e63c9e057617245afab6e556fcafcd</t>
+          <t>cea09e9f1909a922c3be4064aff3c7a8a4ce42ded5160ac38d3411fc4ea0f570</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -28447,11 +28447,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32894</v>
+        <v>24025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5b9e6eea68c00bfca5c3c3b7b5758d4667b4b690bdf7ac68ff20e496af32dc89</t>
+          <t>f606df3a9bef62c4ee7e4dd50726f0a05412212436947e90955ae03069b5d4dd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -28477,11 +28477,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3981</v>
+        <v>3774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>58a5e81a22f751c57c6c4f35696b001f6a21d55fa2b4bd95eb6e52aef4fb4677</t>
+          <t>716da4f6cc3dca5200de5d519c7810f41e5f78348c5aad296ea6f17ec5f00e68</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -28507,11 +28507,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>539</v>
+        <v>466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4936e296d36a191c270ba7f301300fc2ed92621933556e37c2787a41647cc65b</t>
+          <t>db2bf7bbdfd450f30c082ee802c174483ee45e6ab52bb6d131ae3b21fd3e4294</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -28537,11 +28537,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>330</v>
+        <v>154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>422d423d30aa2fcfce90438378b5bca333b390c45a3ed439a4b0645591cde45b</t>
+          <t>4123b461c5b50b0cdba828b9edbb4749cf915ae8aa729087418a9f519dd3a872</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -28567,11 +28567,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1150</v>
+        <v>1004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>78b625a2b3098ef11abc521bddb0ca2539e2890d911f5ab92a2525a352702efb</t>
+          <t>430d1e0a6469dd849916beb2c69ce94e4ac49db453ad2fcbafe6fcf058add73b</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -28597,11 +28597,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6494ff971f76a491d3b8ba704fd099399efb0bde891205446bb6d1977dd747e9</t>
+          <t>a1876abcee893ccceed0ccbd982f3af76242bee8cfe9ce41af3a929ec3117f94</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8069</v>
+        <v>7432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5116</v>
+        <v>4246</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>288992</v>
+        <v>255873</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32574</v>
+        <v>28384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4479</v>
+        <v>4229</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>532</v>
+        <v>369</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1156</v>
+        <v>1056</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,11 +1839,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>28324</v>
+        <v>0</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9897,7 +9897,7 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>25483</v>
+        <v>0</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>0</v>
+        <v>9131</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>22532</v>
+        <v>0</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14283,11 +14283,11 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14351,11 +14351,11 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14385,11 +14385,11 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14453,11 +14453,11 @@
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,7 +17241,7 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0</v>
+        <v>26312</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
@@ -17955,11 +17955,11 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18465,7 +18465,7 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>0</v>
+        <v>9414</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19995,7 +19995,7 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21219,7 +21219,7 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
@@ -21899,11 +21899,11 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21933,11 +21933,11 @@
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>11063</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23361,7 +23361,7 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>1184</v>
+        <v>0</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>30616</v>
+        <v>0</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23973,7 +23973,7 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24313,11 +24313,11 @@
         <v>1</v>
       </c>
       <c r="G694" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24347,11 +24347,11 @@
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24381,11 +24381,11 @@
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24449,11 +24449,11 @@
         <v>1</v>
       </c>
       <c r="G698" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24483,11 +24483,11 @@
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24585,7 +24585,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25197,11 +25197,11 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26421,11 +26421,11 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26455,11 +26455,11 @@
         <v>1</v>
       </c>
       <c r="G757" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26489,11 +26489,11 @@
         <v>1</v>
       </c>
       <c r="G758" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26523,11 +26523,11 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26727,7 +26727,7 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>0</v>
+        <v>26935</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27339,7 +27339,7 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -27407,11 +27407,11 @@
         <v>1</v>
       </c>
       <c r="G785" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27441,11 +27441,11 @@
         <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27509,11 +27509,11 @@
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27543,11 +27543,11 @@
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27679,11 +27679,11 @@
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27713,11 +27713,11 @@
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27747,11 +27747,11 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27951,11 +27951,11 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27985,11 +27985,11 @@
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28019,11 +28019,11 @@
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28053,11 +28053,11 @@
         <v>1</v>
       </c>
       <c r="G804" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28121,11 +28121,11 @@
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>0</v>
+        <v>1301</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28155,11 +28155,11 @@
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28223,11 +28223,11 @@
         <v>1</v>
       </c>
       <c r="G809" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28257,7 +28257,7 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28663,11 +28663,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8069</v>
+        <v>7432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71c0b3a956be1a238c3bd53560746104ea5522adc5245fb35088bb402f57f1ef</t>
+          <t>254acd0cccd7995ef787b5b1812d44adb46656884ee59b84b660c394b96cddbd</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -28693,11 +28693,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5116</v>
+        <v>4246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>94f9e701a6c620c5bca651a4771502788c3b46d4677b0b5ac1dfda86a33335fa</t>
+          <t>696e3c57f63f9491f50bc8b9c6b04de1f9ee2d98263ef83d4646360ac2e09f0f</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -28723,11 +28723,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>288992</v>
+        <v>255873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cdc18c77d9a4ef1a1183479144fe9ba0241ade798c0851b9f356b548bfad97b3</t>
+          <t>7fd23f5c51dcbdc8a81e4a13f1fa4decad0366936db33c827dc5bc2df91915fa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -28753,11 +28753,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32574</v>
+        <v>28384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dd0ee3c2d2a49cd55ab85c4cde31af3301997660c666f08b506826272e4e337e</t>
+          <t>b8f7903d900dc776a57d2fd9d515f3b933789929e9d32fa5a703fbea9ddf4b43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -28783,11 +28783,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4479</v>
+        <v>4229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>c91b4f6ee23946fc4e88ddf59bd87fe1638cd589b51758212428d72b0d2756fa</t>
+          <t>a4ae9f49fe2732dbf47caf71b194ed1fcc5ea07520f59796a502701bd0466856</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -28813,11 +28813,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>532</v>
+        <v>369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>c50f64d576895316c302d4ec528fa1ab81d1085c93c01d9c7d7d0aba5a755480</t>
+          <t>5db1dec8ebf7b6c3f7d6b86548c26e330aa1f0640f9fd781a1a22ec482509533</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -28843,11 +28843,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31bdf051a4a8a95cc79db69ba2f0f54742718d291c9c8d5f058eef3126b4b6a5</t>
+          <t>4a86113c44fb326c94a3737e8b6f1e0122d8a32bac662849c411489e997d5316</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -28873,11 +28873,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1156</v>
+        <v>1056</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9fa664e2b2e39a306906b0e896ab3da6e5652ea56a9e467ce445d9244cb1ab9d</t>
+          <t>39bc984f5cf365f8d662469a79ad81420bbc6f98b08877352ca48d7b42e49ef7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -28903,11 +28903,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>646222e85b64c5c7d0007141d20eb485dede0c52c69983cd8d4fa5c1e89e4979</t>
+          <t>2f370f04e7a1b1e1e434f4de2799a8f2f442736ae1b27ce22a12a9f9901340c0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6712</v>
+        <v>7709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3479</v>
+        <v>5191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>143760</v>
+        <v>290609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24253</v>
+        <v>30651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3911</v>
+        <v>4723</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>368</v>
+        <v>607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>988</v>
+        <v>1186</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>376</v>
+        <v>544</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>28324</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>9347</v>
+        <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>981</v>
+        <v>0</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>25483</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>9131</v>
+        <v>0</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>22532</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14283,11 +14283,11 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>29916</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>1116</v>
+        <v>0</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>25022</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,7 +17241,7 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0</v>
+        <v>26312</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,11 +17853,11 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17887,11 +17887,11 @@
         <v>1</v>
       </c>
       <c r="G505" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>0</v>
+        <v>9414</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,11 +19077,11 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>28253</v>
+        <v>0</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,7 +19383,7 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>1016</v>
+        <v>0</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22749,7 +22749,7 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>0</v>
+        <v>1184</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>30616</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23973,7 +23973,7 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25095,11 +25095,11 @@
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25197,11 +25197,11 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25231,11 +25231,11 @@
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25265,11 +25265,11 @@
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25299,11 +25299,11 @@
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25333,11 +25333,11 @@
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>21955</v>
+        <v>0</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25367,11 +25367,11 @@
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25401,11 +25401,11 @@
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25503,7 +25503,7 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26421,11 +26421,11 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26455,11 +26455,11 @@
         <v>1</v>
       </c>
       <c r="G757" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26489,11 +26489,11 @@
         <v>1</v>
       </c>
       <c r="G758" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26523,11 +26523,11 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>0</v>
+        <v>26935</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27339,11 +27339,11 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27373,11 +27373,11 @@
         <v>1</v>
       </c>
       <c r="G784" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27407,11 +27407,11 @@
         <v>1</v>
       </c>
       <c r="G785" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27441,11 +27441,11 @@
         <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27509,11 +27509,11 @@
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27543,11 +27543,11 @@
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27645,7 +27645,7 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
@@ -27985,11 +27985,11 @@
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28019,11 +28019,11 @@
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28733,11 +28733,11 @@
         <v>1</v>
       </c>
       <c r="G824" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29039,11 +29039,11 @@
         <v>1</v>
       </c>
       <c r="G833" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29073,11 +29073,11 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29175,11 +29175,11 @@
         <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29209,11 +29209,11 @@
         <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29275,11 +29275,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6712</v>
+        <v>7709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2c40ac4a491129b950011db928d21217dc3e1cd59129e18dcd1a173f24619b1a</t>
+          <t>c17da7ca57c3f7f25851104e5baabfc11de6db201ccc05a3b6266faab9d9136d</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -29305,11 +29305,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3479</v>
+        <v>5191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>e180633f56ae8a9ce905ded6bbb0a35694f6e0b14e71922c72eb920d64c0c961</t>
+          <t>33c1e3a3365dd94b65010ac641d631af894fc91fc7d2228bb39ea8fce9351ee0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -29335,11 +29335,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>143760</v>
+        <v>290609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>e8a2faed0a36c95faab9222eb109e26c62c6c72d8a50ef1e1ec3e4dd0bb5f399</t>
+          <t>ae5e29004d4bdaa294ba7433809d75c7b761239c3ffbfae89a483c0ff353717e</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -29365,11 +29365,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24253</v>
+        <v>30651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9a666edf20adbae910baf0c9b9de2abc9d2abd3770adf9eb4a274154a7dc6fcf</t>
+          <t>29ec6c9449fd35831df27b871d1f079cb38b8d3a791d1830e63c75c8e045c385</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -29395,11 +29395,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3911</v>
+        <v>4723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>04fb81ad0f5665c6405565fe8d1cc8e2f9b6c9195cb81551fcf0651352f159c3</t>
+          <t>a4bdab34cc7a83a2d6e64dd5ac002868c279f5693aa1bd618edfc9f8010f67e9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -29425,11 +29425,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>368</v>
+        <v>607</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>b0ef08e913861e56a6f3270d6d3390c118c33228654bee3dbd3ffd007a9241b2</t>
+          <t>beeb1db2b5f69a78e39664b82b657fc29fa95b502bc0896e14db04fbbede037a</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>a37e303db6542dbb58390b6a2c843517c22fc36cad43c8d7fe83d5fc5d1c6e23</t>
+          <t>3a553f5b76820995b76feb6cd6b0e5b2ff9f2bfefb595c3a3027b98ddee1bd8f</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -29485,11 +29485,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>988</v>
+        <v>1186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>a1c9f3d368813d8f1668fbd83399a44b55a14f26d591fc8e2929d9b836084c98</t>
+          <t>ad95625459bff232fe717113fab4757b4af3b82fc0e8ab7d38c43f8be2439d8f</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -29515,11 +29515,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>376</v>
+        <v>544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1cb61ef490f4ad77c582c4c3841c2560a3c187b4fa6e60a3185a20426beee28b</t>
+          <t>02955723696763fdac47619dd8396436dbe692a942fbab2b9710244770ddf2a7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7343</v>
+        <v>7534</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4218</v>
+        <v>5276</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>136080</v>
+        <v>272443</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26620</v>
+        <v>31113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4192</v>
+        <v>4830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>512</v>
+        <v>620</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6089,11 +6089,11 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6123,11 +6123,11 @@
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>9347</v>
+        <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>25483</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12957,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13875,7 +13875,7 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14283,11 +14283,11 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>29916</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>25022</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0</v>
+        <v>26312</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,11 +17853,11 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17887,11 +17887,11 @@
         <v>1</v>
       </c>
       <c r="G505" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17921,11 +17921,11 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>9414</v>
+        <v>0</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,11 +19077,11 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,7 +19995,7 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>1184</v>
+        <v>0</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,7 +24279,7 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>617</v>
+        <v>0</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25197,11 +25197,11 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25231,11 +25231,11 @@
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25265,11 +25265,11 @@
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25299,11 +25299,11 @@
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25333,11 +25333,11 @@
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>0</v>
+        <v>21955</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25367,11 +25367,11 @@
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25401,11 +25401,11 @@
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25503,11 +25503,11 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26115,7 +26115,7 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27339,7 +27339,7 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27951,11 +27951,11 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27985,11 +27985,11 @@
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28019,11 +28019,11 @@
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>24933</v>
+        <v>0</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28427,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="G816" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28495,11 +28495,11 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28563,7 +28563,7 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
@@ -29209,11 +29209,11 @@
         <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -30263,11 +30263,11 @@
         <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>972</v>
+        <v>0</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30297,11 +30297,11 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30433,11 +30433,11 @@
         <v>1</v>
       </c>
       <c r="G874" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30467,11 +30467,11 @@
         <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30705,11 +30705,11 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30805,11 +30805,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7343</v>
+        <v>7534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>88f52596e81218ef566e8eeb0dc487eb715253d2099f383c98071fc06591bdf6</t>
+          <t>559bb2e9641a80c747d79ef31a2aa7604d3f0cf556635ea330c26f1aa4deb1f4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -30835,11 +30835,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4218</v>
+        <v>5276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>d5b5163f563c8a75c7aaee682d0aad4b9325be2c3865852357fd77f19f649416</t>
+          <t>09046241f3463d88cc8eed7e2d8b75778bcb7deccce0479b6481bf8a50525604</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -30865,11 +30865,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>136080</v>
+        <v>272443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4c3607eca7681639f3fffdfcf9ca85e46e69a34531863611ceb90a27163df3d4</t>
+          <t>cb1feaa8268d1d38e958ecbc5872fb773bdaead0af7856d6d175371495efe342</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -30895,11 +30895,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26620</v>
+        <v>31113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1be1956b2e0d7a0993365fd81f06efcebeedc0f8e349154467e70493de0d0cc9</t>
+          <t>d224d92298a9a5be680a2a7c682ff4dcdf7e090d5ee7c9d4dfacae3ebbabea3d</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -30925,11 +30925,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4192</v>
+        <v>4830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bc06b792d5fdf85681be3be5c767842eee60bf2c69d0c7a65d4a26157f308647</t>
+          <t>2e3e27bbfd286da2b8f5dccdba0b746cd222775600380bb66d63a30d90741d09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -30955,11 +30955,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>316</v>
+        <v>576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>a0b0bcf5ecb45a6627a6e5e6c140fdcdb36fd3d65c2caf7b62e665397883fe45</t>
+          <t>5c9dadd10990a47d0065b4dae9363853cf17561198a4dc5858ad5fc58a9eee8e</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -30985,11 +30985,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>159279def47f9565d1215c51c15d545fb89e31ab3d74adaa239fa9181bfc79ab</t>
+          <t>e085767f876faef97fb64e92d28a8ec48d99415046e1dadba2a076e8dc7e0b62</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31015,11 +31015,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>a19692461aa65bc11e87e9388221e84f9c33494972a50d75536737523849fe8c</t>
+          <t>2a4d03e7388f45a6b340906bf60de04346f0cf724119db0c3d41239e535eb587</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31045,11 +31045,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>512</v>
+        <v>620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>c0daa7a17711cd431f948e43ead1f8805de0a728561809261e94b344c84fe869</t>
+          <t>191ea70e89b6d0812ba68c4a5a25eaec00582294089c8a9cb334ac58c20f36f1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7534</v>
+        <v>7546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5276</v>
+        <v>5403</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>272443</v>
+        <v>329068</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31113</v>
+        <v>32377</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4830</v>
+        <v>4604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1126</v>
+        <v>1150</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H883"/>
+  <dimension ref="A1:H901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6089,11 +6089,11 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6123,11 +6123,11 @@
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10203,7 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>0</v>
+        <v>9131</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>22532</v>
+        <v>0</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15099,11 +15099,11 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>0</v>
+        <v>1116</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20199,11 +20199,11 @@
         <v>1</v>
       </c>
       <c r="G573" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>0</v>
+        <v>29593</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         <v>1</v>
       </c>
       <c r="G637" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22783,11 +22783,11 @@
         <v>1</v>
       </c>
       <c r="G649" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>0</v>
+        <v>1184</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>30616</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
@@ -25265,11 +25265,11 @@
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25299,11 +25299,11 @@
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25333,11 +25333,11 @@
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>21955</v>
+        <v>0</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25367,11 +25367,11 @@
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25401,11 +25401,11 @@
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25503,11 +25503,11 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25537,11 +25537,11 @@
         <v>1</v>
       </c>
       <c r="G730" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25571,11 +25571,11 @@
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25605,11 +25605,11 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25673,11 +25673,11 @@
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,7 +26115,7 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27339,7 +27339,7 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -27747,11 +27747,11 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27815,11 +27815,11 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>811</v>
+        <v>0</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27951,11 +27951,11 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27985,11 +27985,11 @@
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28019,11 +28019,11 @@
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28257,11 +28257,11 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>0</v>
+        <v>24933</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28427,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="G816" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28495,11 +28495,11 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28563,7 +28563,7 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
@@ -29039,11 +29039,11 @@
         <v>1</v>
       </c>
       <c r="G833" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29073,11 +29073,11 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29175,11 +29175,11 @@
         <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29481,11 +29481,11 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29515,11 +29515,11 @@
         <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29549,11 +29549,11 @@
         <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
@@ -30742,6 +30742,618 @@
         <v>14</v>
       </c>
       <c r="H883" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B884" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C884" t="n">
+        <v>11383</v>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F884" t="b">
+        <v>1</v>
+      </c>
+      <c r="G884" t="n">
+        <v>127</v>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>race_control</t>
+        </is>
+      </c>
+      <c r="B885" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C885" t="n">
+        <v>11383</v>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F885" t="b">
+        <v>1</v>
+      </c>
+      <c r="G885" t="n">
+        <v>159</v>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B886" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C886" t="n">
+        <v>11383</v>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F886" t="b">
+        <v>1</v>
+      </c>
+      <c r="G886" t="n">
+        <v>6839</v>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="B887" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C887" t="n">
+        <v>11383</v>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F887" t="b">
+        <v>1</v>
+      </c>
+      <c r="G887" t="n">
+        <v>206</v>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="B888" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C888" t="n">
+        <v>11383</v>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F888" t="b">
+        <v>1</v>
+      </c>
+      <c r="G888" t="n">
+        <v>76</v>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>pit</t>
+        </is>
+      </c>
+      <c r="B889" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C889" t="n">
+        <v>11383</v>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F889" t="b">
+        <v>1</v>
+      </c>
+      <c r="G889" t="n">
+        <v>54</v>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>starting_grid</t>
+        </is>
+      </c>
+      <c r="B890" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C890" t="n">
+        <v>11383</v>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F890" t="b">
+        <v>1</v>
+      </c>
+      <c r="G890" t="n">
+        <v>0</v>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>drivers</t>
+        </is>
+      </c>
+      <c r="B891" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C891" t="n">
+        <v>11383</v>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F891" t="b">
+        <v>1</v>
+      </c>
+      <c r="G891" t="n">
+        <v>22</v>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>team_radio</t>
+        </is>
+      </c>
+      <c r="B892" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C892" t="n">
+        <v>11383</v>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F892" t="b">
+        <v>1</v>
+      </c>
+      <c r="G892" t="n">
+        <v>20</v>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B893" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C893" t="n">
+        <v>11384</v>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F893" t="b">
+        <v>1</v>
+      </c>
+      <c r="G893" t="n">
+        <v>88</v>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>race_control</t>
+        </is>
+      </c>
+      <c r="B894" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C894" t="n">
+        <v>11384</v>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F894" t="b">
+        <v>1</v>
+      </c>
+      <c r="G894" t="n">
+        <v>64</v>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B895" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C895" t="n">
+        <v>11384</v>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F895" t="b">
+        <v>1</v>
+      </c>
+      <c r="G895" t="n">
+        <v>0</v>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="B896" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C896" t="n">
+        <v>11384</v>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F896" t="b">
+        <v>1</v>
+      </c>
+      <c r="G896" t="n">
+        <v>1032</v>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="B897" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C897" t="n">
+        <v>11384</v>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F897" t="b">
+        <v>1</v>
+      </c>
+      <c r="G897" t="n">
+        <v>103</v>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>pit</t>
+        </is>
+      </c>
+      <c r="B898" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C898" t="n">
+        <v>11384</v>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F898" t="b">
+        <v>0</v>
+      </c>
+      <c r="G898" t="n">
+        <v>0</v>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>skipped_not_applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>starting_grid</t>
+        </is>
+      </c>
+      <c r="B899" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C899" t="n">
+        <v>11384</v>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F899" t="b">
+        <v>1</v>
+      </c>
+      <c r="G899" t="n">
+        <v>0</v>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>drivers</t>
+        </is>
+      </c>
+      <c r="B900" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C900" t="n">
+        <v>11384</v>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F900" t="b">
+        <v>1</v>
+      </c>
+      <c r="G900" t="n">
+        <v>22</v>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>team_radio</t>
+        </is>
+      </c>
+      <c r="B901" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C901" t="n">
+        <v>11384</v>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F901" t="b">
+        <v>1</v>
+      </c>
+      <c r="G901" t="n">
+        <v>12</v>
+      </c>
+      <c r="H901" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -30805,11 +31417,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7534</v>
+        <v>7546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>559bb2e9641a80c747d79ef31a2aa7604d3f0cf556635ea330c26f1aa4deb1f4</t>
+          <t>adb098ede6fb9405c6fe3c952bf117d371b89aa08a22270e8d8b2f0b4a6c7a95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -30835,11 +31447,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5276</v>
+        <v>5403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09046241f3463d88cc8eed7e2d8b75778bcb7deccce0479b6481bf8a50525604</t>
+          <t>ad8831f6ff3dd90747fbc2fd60d9c7259958e86ec553891b5575597c2198e931</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -30865,11 +31477,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>272443</v>
+        <v>329068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cb1feaa8268d1d38e958ecbc5872fb773bdaead0af7856d6d175371495efe342</t>
+          <t>76390ebdad08c89d3a25030c39f04573dd19f96828ae17134060532a65410019</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -30895,11 +31507,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31113</v>
+        <v>32377</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>d224d92298a9a5be680a2a7c682ff4dcdf7e090d5ee7c9d4dfacae3ebbabea3d</t>
+          <t>7003ff5e902a63cee8167649ce3a4df13486eda4452f3752ae2c9eac90fc359a</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -30925,11 +31537,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4830</v>
+        <v>4604</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2e3e27bbfd286da2b8f5dccdba0b746cd222775600380bb66d63a30d90741d09</t>
+          <t>d8d7bf7a549f6737c386224c69068b0a228f2d28e5daf68c338f9643ee97cdd3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -30955,11 +31567,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5c9dadd10990a47d0065b4dae9363853cf17561198a4dc5858ad5fc58a9eee8e</t>
+          <t>8df4a4d5592376d1b8a0caf57225993a2c6266286f654a8597b2602be9586de6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -30985,11 +31597,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>e085767f876faef97fb64e92d28a8ec48d99415046e1dadba2a076e8dc7e0b62</t>
+          <t>ec335865ff639b3f34d6fa3e46f908b57c4c1246d3ac8b3327974662b7a1ab01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31015,11 +31627,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1126</v>
+        <v>1150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2a4d03e7388f45a6b340906bf60de04346f0cf724119db0c3d41239e535eb587</t>
+          <t>c848130a7e7c12be828d52dd90b863c4dcdff5090c1e8c50cf085f62ba9d4610</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31045,11 +31657,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>191ea70e89b6d0812ba68c4a5a25eaec00582294089c8a9cb334ac58c20f36f1</t>
+          <t>826cd2c9e8b3364e6f1aa0b2edd074a1ea6833c5061393976cf4f8c0aa0fed77</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -31074,7 +31686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37823,6 +38435,142 @@
         <v>1</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>11383</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-10-10T09:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-10-10T10:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1296</v>
+      </c>
+      <c r="G100" t="n">
+        <v>61</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>157</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Marina Bay</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O100" t="b">
+        <v>0</v>
+      </c>
+      <c r="P100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>11384</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-10-10T13:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-10-10T14:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1296</v>
+      </c>
+      <c r="G101" t="n">
+        <v>61</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>157</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Marina Bay</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O101" t="b">
+        <v>0</v>
+      </c>
+      <c r="P101" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8225</v>
+        <v>7526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5669</v>
+        <v>4982</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>351787</v>
+        <v>232475</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40547</v>
+        <v>34054</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5035</v>
+        <v>4783</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>619</v>
+        <v>566</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>396</v>
+        <v>198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1320</v>
+        <v>1133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>578</v>
+        <v>644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>22276</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>28324</v>
+        <v>0</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>9347</v>
+        <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14283,11 +14283,11 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14351,11 +14351,11 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14385,11 +14385,11 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14453,11 +14453,11 @@
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,7 +17241,7 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
@@ -17853,11 +17853,11 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17887,11 +17887,11 @@
         <v>1</v>
       </c>
       <c r="G505" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17921,11 +17921,11 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17955,11 +17955,11 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>28253</v>
+        <v>0</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>23116</v>
+        <v>0</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,7 +21525,7 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>29593</v>
+        <v>0</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>536</v>
+        <v>0</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         <v>1</v>
       </c>
       <c r="G637" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22749,7 +22749,7 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>1184</v>
+        <v>0</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>30616</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,7 +24279,7 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>617</v>
+        <v>0</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25061,11 @@
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25095,11 +25095,11 @@
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26285,11 +26285,11 @@
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26319,11 +26319,11 @@
         <v>1</v>
       </c>
       <c r="G753" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27339,11 +27339,11 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27373,11 +27373,11 @@
         <v>1</v>
       </c>
       <c r="G784" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27407,11 +27407,11 @@
         <v>1</v>
       </c>
       <c r="G785" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27441,11 +27441,11 @@
         <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27509,11 +27509,11 @@
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27543,11 +27543,11 @@
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27645,7 +27645,7 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
@@ -28121,11 +28121,11 @@
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>1301</v>
+        <v>0</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28155,11 +28155,11 @@
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28223,11 +28223,11 @@
         <v>1</v>
       </c>
       <c r="G809" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28257,11 +28257,11 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28733,11 +28733,11 @@
         <v>1</v>
       </c>
       <c r="G824" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28767,11 +28767,11 @@
         <v>1</v>
       </c>
       <c r="G825" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29787,11 +29787,11 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30569,11 +30569,11 @@
         <v>1</v>
       </c>
       <c r="G878" t="n">
-        <v>0</v>
+        <v>998</v>
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30603,11 +30603,11 @@
         <v>1</v>
       </c>
       <c r="G879" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30637,11 +30637,11 @@
         <v>1</v>
       </c>
       <c r="G880" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30671,11 +30671,11 @@
         <v>1</v>
       </c>
       <c r="G881" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30705,11 +30705,11 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31011,11 +31011,11 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31045,11 +31045,11 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31079,11 +31079,11 @@
         <v>1</v>
       </c>
       <c r="G893" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31113,11 +31113,11 @@
         <v>1</v>
       </c>
       <c r="G894" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31181,11 +31181,11 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31317,7 +31317,7 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
@@ -31417,11 +31417,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8225</v>
+        <v>7526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>95e3a34d3ba8dfd83f4c9ed1b94b118d7c994f1eff4d6d625e28b20a10b8caa9</t>
+          <t>3819cb8b3545672ff9c6ed6de450597cabc9a80413ff3138a923c254668ce4f5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31447,11 +31447,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5669</v>
+        <v>4982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>aa9ef673b4b20ec8e2b1903d5fb6e6402e007c14628c9eb00ae688e391c5349c</t>
+          <t>79f4a2fa8a89589b31e7cc0b5ce0eb29251530a1b0715552c669c2c74778ee9c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31477,11 +31477,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>351787</v>
+        <v>232475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>84198d10be8565c21576ecda9153860397a42febd7d7d3c6ab9d4f428ced7586</t>
+          <t>d39dd9fa2af74576e5dd1a0ec84d97e76747482eede8dcbf093fb9a2c43b73a0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31507,11 +31507,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40547</v>
+        <v>34054</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>bfeb8b15ab7d3cdf4689c054abf42954bb13d338e2c4a4a80bd03d02d7c3df9a</t>
+          <t>3f6b99d19b52cbc25bec93dd46233a29603b42fdd85e0f0e7ead1c2d62fcf465</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31537,11 +31537,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5035</v>
+        <v>4783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>81c5f2f0a71d607f07fd1f5def0878c840268b0d08f5986a883dfcdd4956c504</t>
+          <t>14ef0807b36b08e83018f39e8708c516d58a8c3c72d0b09ccb8469724bc0d261</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31567,11 +31567,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>619</v>
+        <v>566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8c97e1e659b3c719c8b84834dc73a1959027c7178048897111d3314e0af584d7</t>
+          <t>4686ce78bf759514bf7f7050a9ae749300e92b4b75911bdabbe47ace20ff9eff</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31597,11 +31597,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>396</v>
+        <v>198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5f94046ab8b368f5a08b0299b7c8f4e489530bf947c25dd641c57721d386e772</t>
+          <t>dba5c2ca04b3477552e4746baf367dec094238f4d5cf04fdf6543f748dc25923</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31627,11 +31627,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1320</v>
+        <v>1133</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>fb012c0606dbb99c72fd6b9db33a46020060edb2d65de9509304009d18a8154a</t>
+          <t>07f386613dfb966e288448d7c0fbbfff2b934fd82949897d7e2e1b1850feaa4f</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31657,11 +31657,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>578</v>
+        <v>644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05af2c779919d3d97104d424ab94a4b98f2f826e90d7554b2a46be3c93e1a10b</t>
+          <t>5ea885502380c4d971997ea3f0d8caa6fcdc73205e02c87de30eb27fa9c16d47</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7526</v>
+        <v>7169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4982</v>
+        <v>4287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>232475</v>
+        <v>142812</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34054</v>
+        <v>32668</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4783</v>
+        <v>4566</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>566</v>
+        <v>638</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>198</v>
+        <v>264</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1133</v>
+        <v>1216</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>644</v>
+        <v>521</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>9019</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>20663</v>
+        <v>0</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>524</v>
+        <v>0</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>9347</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>29916</v>
+        <v>0</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
@@ -15099,11 +15099,11 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>1116</v>
+        <v>0</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>25022</v>
+        <v>0</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17853,11 +17853,11 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17887,11 +17887,11 @@
         <v>1</v>
       </c>
       <c r="G505" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17921,11 +17921,11 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17955,11 +17955,11 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>9414</v>
+        <v>0</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>968</v>
+        <v>0</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19077,11 +19077,11 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19689,7 +19689,7 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>734</v>
+        <v>0</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21219,7 +21219,7 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21831,11 +21831,11 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21899,11 +21899,11 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21933,11 +21933,11 @@
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>0</v>
+        <v>29593</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         <v>1</v>
       </c>
       <c r="G637" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22443,7 +22443,7 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>11063</v>
+        <v>0</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25061,11 @@
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25095,11 +25095,11 @@
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25197,11 +25197,11 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,7 +26115,7 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
@@ -26319,11 +26319,11 @@
         <v>1</v>
       </c>
       <c r="G753" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26421,11 +26421,11 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26455,11 +26455,11 @@
         <v>1</v>
       </c>
       <c r="G757" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26489,11 +26489,11 @@
         <v>1</v>
       </c>
       <c r="G758" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26523,11 +26523,11 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>26935</v>
+        <v>0</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27339,7 +27339,7 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -28053,11 +28053,11 @@
         <v>1</v>
       </c>
       <c r="G804" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29481,11 +29481,11 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29515,11 +29515,11 @@
         <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29549,11 +29549,11 @@
         <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29787,11 +29787,11 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29889,11 +29889,11 @@
         <v>1</v>
       </c>
       <c r="G858" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29923,11 +29923,11 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>21448</v>
+        <v>0</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29957,11 +29957,11 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29991,11 +29991,11 @@
         <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30025,11 +30025,11 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30093,11 +30093,11 @@
         <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30127,11 +30127,11 @@
         <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30161,11 +30161,11 @@
         <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30195,11 +30195,11 @@
         <v>1</v>
       </c>
       <c r="G867" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30263,11 +30263,11 @@
         <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>972</v>
+        <v>0</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30297,11 +30297,11 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>0</v>
+        <v>6839</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31011,11 +31011,11 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31045,11 +31045,11 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31079,11 +31079,11 @@
         <v>1</v>
       </c>
       <c r="G893" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31113,11 +31113,11 @@
         <v>1</v>
       </c>
       <c r="G894" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31181,11 +31181,11 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31317,7 +31317,7 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
@@ -31417,11 +31417,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7526</v>
+        <v>7169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3819cb8b3545672ff9c6ed6de450597cabc9a80413ff3138a923c254668ce4f5</t>
+          <t>e32936fe1581d7f7942bf487d9dcdf29276a5d69a2a9be205bdae91168ac1419</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31447,11 +31447,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4982</v>
+        <v>4287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>79f4a2fa8a89589b31e7cc0b5ce0eb29251530a1b0715552c669c2c74778ee9c</t>
+          <t>9f564ae9e8c473913a57410d6d6270041baa74ebcf8a3f51abeb8326fd425d64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31477,11 +31477,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>232475</v>
+        <v>142812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>d39dd9fa2af74576e5dd1a0ec84d97e76747482eede8dcbf093fb9a2c43b73a0</t>
+          <t>cdab3545de8358ba2268b55d442e5698feb720d5b43dea77d572a31f7c276894</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31507,11 +31507,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34054</v>
+        <v>32668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3f6b99d19b52cbc25bec93dd46233a29603b42fdd85e0f0e7ead1c2d62fcf465</t>
+          <t>a6f9904bbff933adbcb9e12942e0ffee9399705a4b26cebfa99c560f66e31ad6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31537,11 +31537,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4783</v>
+        <v>4566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14ef0807b36b08e83018f39e8708c516d58a8c3c72d0b09ccb8469724bc0d261</t>
+          <t>c978c419eafe4ccd48521631431cdc3cbf02cca78ca2708f1e0ef363cdf2fedc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31567,11 +31567,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>566</v>
+        <v>638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4686ce78bf759514bf7f7050a9ae749300e92b4b75911bdabbe47ace20ff9eff</t>
+          <t>3538e3ac87d77bf11db18d1493867e91785d7c3c8f0044d87cd6e7e89eb016cc</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31597,11 +31597,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>198</v>
+        <v>264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dba5c2ca04b3477552e4746baf367dec094238f4d5cf04fdf6543f748dc25923</t>
+          <t>50033817ddeaf3847419a5cbf77a938b69ea33118ae46dab67ed16c251deb898</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31627,11 +31627,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1133</v>
+        <v>1216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>07f386613dfb966e288448d7c0fbbfff2b934fd82949897d7e2e1b1850feaa4f</t>
+          <t>62868370d91d4aa87457dbd5c672b0aa244e0d471057dd6f976916d637e6ad77</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31657,11 +31657,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>644</v>
+        <v>521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5ea885502380c4d971997ea3f0d8caa6fcdc73205e02c87de30eb27fa9c16d47</t>
+          <t>4cd3fa0e164f9c04d74cbe4447d951f781d3ecde8eb979c9f9ae80d523d868b4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7169</v>
+        <v>7475</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4287</v>
+        <v>4821</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>142812</v>
+        <v>304925</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32668</v>
+        <v>33876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4566</v>
+        <v>4793</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1216</v>
+        <v>1187</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H901"/>
+  <dimension ref="A1:H910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6089,11 +6089,11 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6123,11 +6123,11 @@
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6599,11 +6599,11 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>9347</v>
+        <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>25483</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>1449</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,11 +19077,11 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20199,11 +20199,11 @@
         <v>1</v>
       </c>
       <c r="G573" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,7 +21219,7 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>1016</v>
+        <v>0</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25197,11 +25197,11 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26285,11 +26285,11 @@
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>496</v>
+        <v>0</v>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>0</v>
+        <v>26935</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27679,11 +27679,11 @@
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27713,11 +27713,11 @@
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27747,11 +27747,11 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27815,11 +27815,11 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>811</v>
+        <v>0</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27951,11 +27951,11 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27985,11 +27985,11 @@
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28019,11 +28019,11 @@
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>0</v>
+        <v>24933</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28427,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="G816" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28495,11 +28495,11 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29243,11 +29243,11 @@
         <v>1</v>
       </c>
       <c r="G839" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29277,11 +29277,11 @@
         <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29481,11 +29481,11 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29515,11 +29515,11 @@
         <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29549,11 +29549,11 @@
         <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29787,11 +29787,11 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29889,11 +29889,11 @@
         <v>1</v>
       </c>
       <c r="G858" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29923,11 +29923,11 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>0</v>
+        <v>21448</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29957,11 +29957,11 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29991,11 +29991,11 @@
         <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30025,11 +30025,11 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30093,11 +30093,11 @@
         <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30127,11 +30127,11 @@
         <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30161,11 +30161,11 @@
         <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30195,11 +30195,11 @@
         <v>1</v>
       </c>
       <c r="G867" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30263,11 +30263,11 @@
         <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>0</v>
+        <v>972</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30297,11 +30297,11 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>6839</v>
+        <v>0</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31011,11 +31011,11 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31045,11 +31045,11 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31079,11 +31079,11 @@
         <v>1</v>
       </c>
       <c r="G893" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31113,11 +31113,11 @@
         <v>1</v>
       </c>
       <c r="G894" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31181,11 +31181,11 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31317,7 +31317,7 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
@@ -31354,6 +31354,312 @@
         <v>12</v>
       </c>
       <c r="H901" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B902" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C902" t="n">
+        <v>11388</v>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F902" t="b">
+        <v>1</v>
+      </c>
+      <c r="G902" t="n">
+        <v>160</v>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>race_control</t>
+        </is>
+      </c>
+      <c r="B903" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C903" t="n">
+        <v>11388</v>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F903" t="b">
+        <v>1</v>
+      </c>
+      <c r="G903" t="n">
+        <v>155</v>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B904" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C904" t="n">
+        <v>11388</v>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F904" t="b">
+        <v>1</v>
+      </c>
+      <c r="G904" t="n">
+        <v>28131</v>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="B905" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C905" t="n">
+        <v>11388</v>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F905" t="b">
+        <v>1</v>
+      </c>
+      <c r="G905" t="n">
+        <v>396</v>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="B906" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C906" t="n">
+        <v>11388</v>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F906" t="b">
+        <v>1</v>
+      </c>
+      <c r="G906" t="n">
+        <v>47</v>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>pit</t>
+        </is>
+      </c>
+      <c r="B907" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C907" t="n">
+        <v>11388</v>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F907" t="b">
+        <v>1</v>
+      </c>
+      <c r="G907" t="n">
+        <v>25</v>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>starting_grid</t>
+        </is>
+      </c>
+      <c r="B908" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C908" t="n">
+        <v>11388</v>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F908" t="b">
+        <v>1</v>
+      </c>
+      <c r="G908" t="n">
+        <v>0</v>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>drivers</t>
+        </is>
+      </c>
+      <c r="B909" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C909" t="n">
+        <v>11388</v>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F909" t="b">
+        <v>1</v>
+      </c>
+      <c r="G909" t="n">
+        <v>22</v>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>team_radio</t>
+        </is>
+      </c>
+      <c r="B910" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C910" t="n">
+        <v>11388</v>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F910" t="b">
+        <v>1</v>
+      </c>
+      <c r="G910" t="n">
+        <v>32</v>
+      </c>
+      <c r="H910" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -31417,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7169</v>
+        <v>7475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>e32936fe1581d7f7942bf487d9dcdf29276a5d69a2a9be205bdae91168ac1419</t>
+          <t>b21f063f8deaf4af7d50c9c13f8fd7fe7a419ef9139f28c0fdd0eb9d9319e6c8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31447,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4287</v>
+        <v>4821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9f564ae9e8c473913a57410d6d6270041baa74ebcf8a3f51abeb8326fd425d64</t>
+          <t>762cec9bcd33c80ed3643706f35ee2beba764e81003eb7fe622ad87ae84959a3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31477,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>142812</v>
+        <v>304925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cdab3545de8358ba2268b55d442e5698feb720d5b43dea77d572a31f7c276894</t>
+          <t>75b982d2d55476761c88bcaf4ef2e3d63478e3b67c05c1e255cf54f89fdf0051</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31507,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32668</v>
+        <v>33876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>a6f9904bbff933adbcb9e12942e0ffee9399705a4b26cebfa99c560f66e31ad6</t>
+          <t>016a72ef18dd6004570e3b4894602bf75173d660637245e61c9047ac93a8c8f5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31537,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4566</v>
+        <v>4793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>c978c419eafe4ccd48521631431cdc3cbf02cca78ca2708f1e0ef363cdf2fedc</t>
+          <t>7b8c12a3c874e3e7bdce303a596259c1f4ac214e7435d5505bd2b8ca5e2c5a55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31567,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3538e3ac87d77bf11db18d1493867e91785d7c3c8f0044d87cd6e7e89eb016cc</t>
+          <t>9a96f0d28d4299edc846c911484095aaae4d1b2a259a6170d34832ddb1133694</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31597,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>50033817ddeaf3847419a5cbf77a938b69ea33118ae46dab67ed16c251deb898</t>
+          <t>4a038fd2cfc6c88fd5ccc1f809bfb1df1af2f29161b573a7337756f1b1b07dd1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31627,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1216</v>
+        <v>1187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>62868370d91d4aa87457dbd5c672b0aa244e0d471057dd6f976916d637e6ad77</t>
+          <t>1535d6f5804855fe668de1ec1df4ca361b3386600da866596460409acf7d2b1a</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31657,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4cd3fa0e164f9c04d74cbe4447d951f781d3ecde8eb979c9f9ae80d523d868b4</t>
+          <t>b82735e384f981a966a25e248eb81e2e41a2bce6b4303366d678872f9cbde41d</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -31686,7 +31992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38456,7 +38762,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-10T10:00:00+00:00</t>
+          <t>2026-10-10T09:30:00+00:00</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -38519,12 +38825,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:00+00:00</t>
+          <t>2026-10-10T13:00:00+00:00</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-10T14:30:00+00:00</t>
+          <t>2026-10-10T14:00:00+00:00</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -38568,6 +38874,74 @@
         <v>0</v>
       </c>
       <c r="P101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>11388</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-10-11T12:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-10-11T14:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1296</v>
+      </c>
+      <c r="G102" t="n">
+        <v>61</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>157</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Marina Bay</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O102" t="b">
+        <v>0</v>
+      </c>
+      <c r="P102" t="b">
         <v>1</v>
       </c>
     </row>

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7475</v>
+        <v>5345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4821</v>
+        <v>2871</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>304925</v>
+        <v>153752</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33876</v>
+        <v>12423</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4793</v>
+        <v>2623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>625</v>
+        <v>226</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>220</v>
+        <v>66</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1187</v>
+        <v>819</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>627</v>
+        <v>421</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,11 +1839,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>9347</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>981</v>
+        <v>0</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>25483</v>
+        <v>0</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>22532</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14351,11 +14351,11 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14385,11 +14385,11 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14453,11 +14453,11 @@
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>29916</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>982</v>
+        <v>0</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
@@ -19077,11 +19077,11 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>28253</v>
+        <v>0</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19689,7 +19689,7 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>23116</v>
+        <v>0</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20913,7 +20913,7 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22137,7 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22783,11 +22783,11 @@
         <v>1</v>
       </c>
       <c r="G649" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23055,7 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>11063</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>30616</v>
+        <v>0</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24279,7 +24279,7 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
@@ -24313,11 +24313,11 @@
         <v>1</v>
       </c>
       <c r="G694" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24347,11 +24347,11 @@
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24381,11 +24381,11 @@
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24449,11 +24449,11 @@
         <v>1</v>
       </c>
       <c r="G698" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24483,11 +24483,11 @@
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -25231,11 +25231,11 @@
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25265,11 +25265,11 @@
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25299,11 +25299,11 @@
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25333,11 +25333,11 @@
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>21955</v>
+        <v>0</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25367,11 +25367,11 @@
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25401,11 +25401,11 @@
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25503,11 +25503,11 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25537,11 +25537,11 @@
         <v>1</v>
       </c>
       <c r="G730" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25571,11 +25571,11 @@
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25605,11 +25605,11 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25673,11 +25673,11 @@
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>26935</v>
+        <v>0</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27033,7 +27033,7 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27339,11 +27339,11 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27373,11 +27373,11 @@
         <v>1</v>
       </c>
       <c r="G784" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27407,11 +27407,11 @@
         <v>1</v>
       </c>
       <c r="G785" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27441,11 +27441,11 @@
         <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27509,11 +27509,11 @@
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27543,11 +27543,11 @@
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27951,11 +27951,11 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27985,11 +27985,11 @@
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28019,11 +28019,11 @@
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>24933</v>
+        <v>0</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28427,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="G816" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28495,11 +28495,11 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28733,11 +28733,11 @@
         <v>1</v>
       </c>
       <c r="G824" t="n">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28767,11 +28767,11 @@
         <v>1</v>
       </c>
       <c r="G825" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -28903,11 +28903,11 @@
         <v>1</v>
       </c>
       <c r="G829" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28937,11 +28937,11 @@
         <v>1</v>
       </c>
       <c r="G830" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28971,11 +28971,11 @@
         <v>1</v>
       </c>
       <c r="G831" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29039,11 +29039,11 @@
         <v>1</v>
       </c>
       <c r="G833" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29073,11 +29073,11 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29175,11 +29175,11 @@
         <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29209,11 +29209,11 @@
         <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29787,11 +29787,11 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29923,11 +29923,11 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>21448</v>
+        <v>0</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29957,11 +29957,11 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29991,11 +29991,11 @@
         <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30025,11 +30025,11 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30093,11 +30093,11 @@
         <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30127,11 +30127,11 @@
         <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30161,11 +30161,11 @@
         <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30195,11 +30195,11 @@
         <v>1</v>
       </c>
       <c r="G867" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30263,11 +30263,11 @@
         <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>972</v>
+        <v>0</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30297,11 +30297,11 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30433,11 +30433,11 @@
         <v>1</v>
       </c>
       <c r="G874" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30467,11 +30467,11 @@
         <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30501,11 +30501,11 @@
         <v>1</v>
       </c>
       <c r="G876" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30569,11 +30569,11 @@
         <v>1</v>
       </c>
       <c r="G878" t="n">
-        <v>998</v>
+        <v>0</v>
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30603,11 +30603,11 @@
         <v>1</v>
       </c>
       <c r="G879" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30637,11 +30637,11 @@
         <v>1</v>
       </c>
       <c r="G880" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30671,11 +30671,11 @@
         <v>1</v>
       </c>
       <c r="G881" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30705,7 +30705,7 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>0</v>
+        <v>6839</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31317,11 +31317,11 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31351,11 +31351,11 @@
         <v>1</v>
       </c>
       <c r="G901" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>28131</v>
+        <v>0</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31521,11 +31521,11 @@
         <v>1</v>
       </c>
       <c r="G906" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31555,11 +31555,11 @@
         <v>1</v>
       </c>
       <c r="G907" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31623,7 +31623,7 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7475</v>
+        <v>5345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>b21f063f8deaf4af7d50c9c13f8fd7fe7a419ef9139f28c0fdd0eb9d9319e6c8</t>
+          <t>81d8fc31168c731ccfcb032c9120eeb4214b5f8c4d06585fe36d19e8d5f8e17d</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4821</v>
+        <v>2871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>762cec9bcd33c80ed3643706f35ee2beba764e81003eb7fe622ad87ae84959a3</t>
+          <t>49ab1ec0f1acf4ea6138d83bba0c655779fb59a508bab2257509164bb2b300f3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>304925</v>
+        <v>153752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>75b982d2d55476761c88bcaf4ef2e3d63478e3b67c05c1e255cf54f89fdf0051</t>
+          <t>dabe79f66225e165c83457224269eb0c9c59f11effbb3b68dac22c283ddcc2d5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33876</v>
+        <v>12423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>016a72ef18dd6004570e3b4894602bf75173d660637245e61c9047ac93a8c8f5</t>
+          <t>1084f5ff4795a608e7587e574b9b649b4ed892625edae3d54a1a1d2236964885</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4793</v>
+        <v>2623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7b8c12a3c874e3e7bdce303a596259c1f4ac214e7435d5505bd2b8ca5e2c5a55</t>
+          <t>07851048b64f39c6c468e66493372fe2230eb9667940f9f25880734e4feda8a9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>625</v>
+        <v>226</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9a96f0d28d4299edc846c911484095aaae4d1b2a259a6170d34832ddb1133694</t>
+          <t>8af7e7c33a2cc74ef02e911a31d5f52b3c949be8ecfc5b0157c042099ef5f057</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>66</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4a038fd2cfc6c88fd5ccc1f809bfb1df1af2f29161b573a7337756f1b1b07dd1</t>
+          <t>2fde7377c1f02207c4b77076a2bb9dfd396a01d9755d3ac5e4aceb82fae3dd5b</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1187</v>
+        <v>819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1535d6f5804855fe668de1ec1df4ca361b3386600da866596460409acf7d2b1a</t>
+          <t>a2c0857b7366a78b9d520e5463d6176f0adf110c139c7278675cc4a6ddc7ba7c</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>627</v>
+        <v>421</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>b82735e384f981a966a25e248eb81e2e41a2bce6b4303366d678872f9cbde41d</t>
+          <t>5bb962fd55d938d44cdd554f42a2fc943a3e1b9c463a01819b404c28f96b59ed</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5345</v>
+        <v>8181</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2871</v>
+        <v>5606</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>153752</v>
+        <v>340099</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12423</v>
+        <v>34089</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2623</v>
+        <v>4461</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>226</v>
+        <v>694</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>242</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>819</v>
+        <v>1245</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>421</v>
+        <v>649</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,11 +1839,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>22276</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>20663</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6089,11 +6089,11 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6123,11 +6123,11 @@
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6599,11 +6599,11 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>28324</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>9347</v>
+        <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>25483</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>9131</v>
+        <v>0</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14351,11 +14351,11 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14385,11 +14385,11 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14453,11 +14453,11 @@
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>0</v>
+        <v>9414</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>968</v>
+        <v>0</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19689,7 +19689,7 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,7 +20913,7 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>734</v>
+        <v>0</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21831,11 +21831,11 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21899,11 +21899,11 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21933,11 +21933,11 @@
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>29593</v>
+        <v>0</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>536</v>
+        <v>0</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         <v>1</v>
       </c>
       <c r="G637" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22783,11 +22783,11 @@
         <v>1</v>
       </c>
       <c r="G649" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23055,7 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>11063</v>
+        <v>0</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>30616</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25197,11 +25197,11 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25503,11 +25503,11 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25537,11 +25537,11 @@
         <v>1</v>
       </c>
       <c r="G730" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25571,11 +25571,11 @@
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25605,11 +25605,11 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25673,11 +25673,11 @@
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26421,11 +26421,11 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26455,11 +26455,11 @@
         <v>1</v>
       </c>
       <c r="G757" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26489,11 +26489,11 @@
         <v>1</v>
       </c>
       <c r="G758" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26523,11 +26523,11 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>0</v>
+        <v>26935</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27339,11 +27339,11 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27373,11 +27373,11 @@
         <v>1</v>
       </c>
       <c r="G784" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27407,11 +27407,11 @@
         <v>1</v>
       </c>
       <c r="G785" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27441,11 +27441,11 @@
         <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27509,11 +27509,11 @@
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27543,11 +27543,11 @@
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27679,11 +27679,11 @@
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27713,11 +27713,11 @@
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27747,11 +27747,11 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27815,11 +27815,11 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27951,11 +27951,11 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27985,11 +27985,11 @@
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28019,11 +28019,11 @@
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28257,11 +28257,11 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>0</v>
+        <v>24933</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28427,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="G816" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28495,11 +28495,11 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28733,11 +28733,11 @@
         <v>1</v>
       </c>
       <c r="G824" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28767,11 +28767,11 @@
         <v>1</v>
       </c>
       <c r="G825" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -28903,11 +28903,11 @@
         <v>1</v>
       </c>
       <c r="G829" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28937,11 +28937,11 @@
         <v>1</v>
       </c>
       <c r="G830" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28971,11 +28971,11 @@
         <v>1</v>
       </c>
       <c r="G831" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29481,11 +29481,11 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29515,11 +29515,11 @@
         <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29549,11 +29549,11 @@
         <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -29923,11 +29923,11 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>0</v>
+        <v>21448</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30433,11 +30433,11 @@
         <v>1</v>
       </c>
       <c r="G874" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30467,11 +30467,11 @@
         <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30501,11 +30501,11 @@
         <v>1</v>
       </c>
       <c r="G876" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30569,11 +30569,11 @@
         <v>1</v>
       </c>
       <c r="G878" t="n">
-        <v>0</v>
+        <v>998</v>
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30603,11 +30603,11 @@
         <v>1</v>
       </c>
       <c r="G879" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30637,11 +30637,11 @@
         <v>1</v>
       </c>
       <c r="G880" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30705,11 +30705,11 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>6839</v>
+        <v>0</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31011,11 +31011,11 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31045,11 +31045,11 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31079,11 +31079,11 @@
         <v>1</v>
       </c>
       <c r="G893" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31113,11 +31113,11 @@
         <v>1</v>
       </c>
       <c r="G894" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31181,11 +31181,11 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31317,11 +31317,11 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31351,11 +31351,11 @@
         <v>1</v>
       </c>
       <c r="G901" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>0</v>
+        <v>28131</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31521,11 +31521,11 @@
         <v>1</v>
       </c>
       <c r="G906" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31555,11 +31555,11 @@
         <v>1</v>
       </c>
       <c r="G907" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31623,7 +31623,7 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5345</v>
+        <v>8181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>81d8fc31168c731ccfcb032c9120eeb4214b5f8c4d06585fe36d19e8d5f8e17d</t>
+          <t>aa55a4e8f87eaae228985fe1fc8eb95799619e10573bbdcf30252e465f586c8d</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2871</v>
+        <v>5606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49ab1ec0f1acf4ea6138d83bba0c655779fb59a508bab2257509164bb2b300f3</t>
+          <t>6b2969980f65c584a2f669715bfe834ef20e1f9ffc47eecc7baa284538918d32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>153752</v>
+        <v>340099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dabe79f66225e165c83457224269eb0c9c59f11effbb3b68dac22c283ddcc2d5</t>
+          <t>98c8e6bfa373181e4e07dd63715e8f4f3776c1c5b242c32a497bab5d795ec444</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12423</v>
+        <v>34089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1084f5ff4795a608e7587e574b9b649b4ed892625edae3d54a1a1d2236964885</t>
+          <t>cd752b4ceed2d611260899fd7ab8ab7f291fed646553cbda2a58f5ada3503fc5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2623</v>
+        <v>4461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>07851048b64f39c6c468e66493372fe2230eb9667940f9f25880734e4feda8a9</t>
+          <t>8d7a59f94715a486c62041265a4c13882c9347c10e2a3f4a4c9bce6cd89b9a2d</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>226</v>
+        <v>694</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8af7e7c33a2cc74ef02e911a31d5f52b3c949be8ecfc5b0157c042099ef5f057</t>
+          <t>b0e86c91731a43c323d61e2c66a6b143a74ab9b38b2491cc28871d2e001dfde9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>66</v>
+        <v>242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2fde7377c1f02207c4b77076a2bb9dfd396a01d9755d3ac5e4aceb82fae3dd5b</t>
+          <t>5edd091a9a1dd303c18564db97218bdb6944e5abb11e3d2780e77fceaac48ee2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>819</v>
+        <v>1245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>a2c0857b7366a78b9d520e5463d6176f0adf110c139c7278675cc4a6ddc7ba7c</t>
+          <t>2203bae1a5b0f684b4aaced5f179d5192fbb558a8e197d1abe0ffcf67ab8a8e4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>421</v>
+        <v>649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5bb962fd55d938d44cdd554f42a2fc943a3e1b9c463a01819b404c28f96b59ed</t>
+          <t>f3cfce49bd0027e6abe9fae56951a281f5b7383ff0b9c01b4368863f6fa3b233</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8181</v>
+        <v>7635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5606</v>
+        <v>5083</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>340099</v>
+        <v>313109</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34089</v>
+        <v>31461</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4461</v>
+        <v>4350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1245</v>
+        <v>1146</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,11 +1839,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>9019</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>29916</v>
+        <v>0</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>982</v>
+        <v>0</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>9414</v>
+        <v>0</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,11 +19077,11 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19689,7 +19689,7 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>0</v>
+        <v>29593</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22749,7 +22749,7 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,7 +24585,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25197,11 +25197,11 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25231,11 +25231,11 @@
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25265,11 +25265,11 @@
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25299,11 +25299,11 @@
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25333,11 +25333,11 @@
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>0</v>
+        <v>21955</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25367,11 +25367,11 @@
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25401,11 +25401,11 @@
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25503,7 +25503,7 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26285,11 +26285,11 @@
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26319,11 +26319,11 @@
         <v>1</v>
       </c>
       <c r="G753" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>26935</v>
+        <v>0</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27339,7 +27339,7 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -27713,11 +27713,11 @@
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27747,11 +27747,11 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27815,11 +27815,11 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>811</v>
+        <v>0</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28257,7 +28257,7 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28733,11 +28733,11 @@
         <v>1</v>
       </c>
       <c r="G824" t="n">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28767,11 +28767,11 @@
         <v>1</v>
       </c>
       <c r="G825" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28869,11 +28869,11 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28903,11 +28903,11 @@
         <v>1</v>
       </c>
       <c r="G829" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28937,11 +28937,11 @@
         <v>1</v>
       </c>
       <c r="G830" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28971,11 +28971,11 @@
         <v>1</v>
       </c>
       <c r="G831" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29175,11 +29175,11 @@
         <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29209,11 +29209,11 @@
         <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29243,11 +29243,11 @@
         <v>1</v>
       </c>
       <c r="G839" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29277,11 +29277,11 @@
         <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29481,11 +29481,11 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29515,11 +29515,11 @@
         <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29549,11 +29549,11 @@
         <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -29957,11 +29957,11 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29991,11 +29991,11 @@
         <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30025,11 +30025,11 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30093,11 +30093,11 @@
         <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30127,11 +30127,11 @@
         <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30161,11 +30161,11 @@
         <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30195,11 +30195,11 @@
         <v>1</v>
       </c>
       <c r="G867" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30263,11 +30263,11 @@
         <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>0</v>
+        <v>972</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30297,11 +30297,11 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30433,11 +30433,11 @@
         <v>1</v>
       </c>
       <c r="G874" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30467,11 +30467,11 @@
         <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30501,11 +30501,11 @@
         <v>1</v>
       </c>
       <c r="G876" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30569,11 +30569,11 @@
         <v>1</v>
       </c>
       <c r="G878" t="n">
-        <v>998</v>
+        <v>0</v>
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30603,11 +30603,11 @@
         <v>1</v>
       </c>
       <c r="G879" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30637,11 +30637,11 @@
         <v>1</v>
       </c>
       <c r="G880" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30705,11 +30705,11 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>0</v>
+        <v>6839</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31011,7 +31011,7 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31317,11 +31317,11 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31351,11 +31351,11 @@
         <v>1</v>
       </c>
       <c r="G901" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>28131</v>
+        <v>0</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31521,11 +31521,11 @@
         <v>1</v>
       </c>
       <c r="G906" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31555,11 +31555,11 @@
         <v>1</v>
       </c>
       <c r="G907" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31623,7 +31623,7 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8181</v>
+        <v>7635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>aa55a4e8f87eaae228985fe1fc8eb95799619e10573bbdcf30252e465f586c8d</t>
+          <t>6f3b63aa7755a776c505061b3b232aa4122951e7f94849b8492a389b2de215aa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5606</v>
+        <v>5083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6b2969980f65c584a2f669715bfe834ef20e1f9ffc47eecc7baa284538918d32</t>
+          <t>034f9bef8983c2feba8f8ab533dbe81dcd0f4b33ab9485b8e63c89a6ec5b3ed5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>340099</v>
+        <v>313109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>98c8e6bfa373181e4e07dd63715e8f4f3776c1c5b242c32a497bab5d795ec444</t>
+          <t>3ce869925dc85e9645a742c55630bd381a0150bda10153c2c11a74a1191b2545</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34089</v>
+        <v>31461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cd752b4ceed2d611260899fd7ab8ab7f291fed646553cbda2a58f5ada3503fc5</t>
+          <t>66950b2db5009e9be193cfb2747e57046957dd19162fed42660bac5584bc1bc2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4461</v>
+        <v>4350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8d7a59f94715a486c62041265a4c13882c9347c10e2a3f4a4c9bce6cd89b9a2d</t>
+          <t>58affe387de5308a37e96008928fe0674652c3c9b807a03ef665d7fc74d46fcc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>b0e86c91731a43c323d61e2c66a6b143a74ab9b38b2491cc28871d2e001dfde9</t>
+          <t>3e945734de838ad59705ecb39b85c993c3846aacd8d958b88b7984497a4b6911</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5edd091a9a1dd303c18564db97218bdb6944e5abb11e3d2780e77fceaac48ee2</t>
+          <t>73a6e9a5bd2f7603a0a3534ffcb8f58ae6123ab5255df2d53d00519a400b75b7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1245</v>
+        <v>1146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2203bae1a5b0f684b4aaced5f179d5192fbb558a8e197d1abe0ffcf67ab8a8e4</t>
+          <t>f6e50cf68286817f285988d1447950dab09fae3cab5960711ff8891ab913d89f</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>f3cfce49bd0027e6abe9fae56951a281f5b7383ff0b9c01b4368863f6fa3b233</t>
+          <t>71915db10c3d041a8f2272f890be459687d9c56b6628d957ab8a920915f6a91e</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7635</v>
+        <v>8233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5083</v>
+        <v>4816</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>313109</v>
+        <v>285711</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31461</v>
+        <v>33129</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4350</v>
+        <v>4338</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>690</v>
+        <v>612</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>22276</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>28324</v>
+        <v>0</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>1449</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14351,11 +14351,11 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14385,11 +14385,11 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14453,11 +14453,11 @@
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>29916</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>25022</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,7 +19995,7 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
@@ -20199,11 +20199,11 @@
         <v>1</v>
       </c>
       <c r="G573" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>23116</v>
+        <v>0</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>734</v>
+        <v>0</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21219,7 +21219,7 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>29593</v>
+        <v>0</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22749,7 +22749,7 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>11063</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>30616</v>
+        <v>0</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23973,7 +23973,7 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24313,11 +24313,11 @@
         <v>1</v>
       </c>
       <c r="G694" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24347,11 +24347,11 @@
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24381,11 +24381,11 @@
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24449,11 +24449,11 @@
         <v>1</v>
       </c>
       <c r="G698" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24483,11 +24483,11 @@
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24585,7 +24585,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>617</v>
+        <v>0</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -25503,11 +25503,11 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25537,11 +25537,11 @@
         <v>1</v>
       </c>
       <c r="G730" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25571,11 +25571,11 @@
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25605,11 +25605,11 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25673,11 +25673,11 @@
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26285,11 +26285,11 @@
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>496</v>
+        <v>0</v>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26319,11 +26319,11 @@
         <v>1</v>
       </c>
       <c r="G753" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27339,7 +27339,7 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27679,11 +27679,11 @@
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27951,11 +27951,11 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27985,11 +27985,11 @@
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28019,11 +28019,11 @@
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28053,11 +28053,11 @@
         <v>1</v>
       </c>
       <c r="G804" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28121,11 +28121,11 @@
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>0</v>
+        <v>1301</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28155,11 +28155,11 @@
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28223,11 +28223,11 @@
         <v>1</v>
       </c>
       <c r="G809" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28257,7 +28257,7 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28869,11 +28869,11 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28903,11 +28903,11 @@
         <v>1</v>
       </c>
       <c r="G829" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28937,11 +28937,11 @@
         <v>1</v>
       </c>
       <c r="G830" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28971,11 +28971,11 @@
         <v>1</v>
       </c>
       <c r="G831" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29039,11 +29039,11 @@
         <v>1</v>
       </c>
       <c r="G833" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29073,11 +29073,11 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29175,7 +29175,7 @@
         <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30433,11 +30433,11 @@
         <v>1</v>
       </c>
       <c r="G874" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30467,11 +30467,11 @@
         <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30705,11 +30705,11 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>6839</v>
+        <v>0</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31011,7 +31011,7 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31317,11 +31317,11 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31351,11 +31351,11 @@
         <v>1</v>
       </c>
       <c r="G901" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>0</v>
+        <v>28131</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31623,11 +31623,11 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31657,11 +31657,11 @@
         <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7635</v>
+        <v>8233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6f3b63aa7755a776c505061b3b232aa4122951e7f94849b8492a389b2de215aa</t>
+          <t>349cb152897646c5001440f4a2229504daee8898f5bfef793234e313b4c20e6b</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5083</v>
+        <v>4816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>034f9bef8983c2feba8f8ab533dbe81dcd0f4b33ab9485b8e63c89a6ec5b3ed5</t>
+          <t>260427654b84f7eab8a27e86bca3cf12fc8fe54047b9c8dcbd6d914e6befcc8a</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>313109</v>
+        <v>285711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3ce869925dc85e9645a742c55630bd381a0150bda10153c2c11a74a1191b2545</t>
+          <t>f726e0fa5fc4e02eaca559cf6e4c6f44e6468abe52e53734e819afeac09f7258</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31461</v>
+        <v>33129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>66950b2db5009e9be193cfb2747e57046957dd19162fed42660bac5584bc1bc2</t>
+          <t>314764c1cdf5d0070d5a8cff529e7c2c91c17aabc4148fc4ac72af6a521e2292</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4350</v>
+        <v>4338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>58affe387de5308a37e96008928fe0674652c3c9b807a03ef665d7fc74d46fcc</t>
+          <t>60dec5766018abb9b617a4e4630a67b41a59d533e77392a91264202fc11e0a1e</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>690</v>
+        <v>612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3e945734de838ad59705ecb39b85c993c3846aacd8d958b88b7984497a4b6911</t>
+          <t>493022c1084871c64a1193d45deaaccd44522cbc46df77110adef602a273792d</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>73a6e9a5bd2f7603a0a3534ffcb8f58ae6123ab5255df2d53d00519a400b75b7</t>
+          <t>03b6373a65c114d64165ecf22b53854506fedf9065b816763f4cb2d1bfbea18a</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>f6e50cf68286817f285988d1447950dab09fae3cab5960711ff8891ab913d89f</t>
+          <t>b34534c0a9f1fe02db0d24e3adcdfed0ec4ee76f945aafa09760f4c60afd7616</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71915db10c3d041a8f2272f890be459687d9c56b6628d957ab8a920915f6a91e</t>
+          <t>815c356689b4f7c995e4caeac2601dd06ee173db8b82c988e348acfa17876f9a</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8233</v>
+        <v>7680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4816</v>
+        <v>5074</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>285711</v>
+        <v>289688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33129</v>
+        <v>33126</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4338</v>
+        <v>4558</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>612</v>
+        <v>497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1143</v>
+        <v>1209</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>640</v>
+        <v>573</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4389,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>28324</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>25483</v>
+        <v>0</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>0</v>
+        <v>9131</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>22532</v>
+        <v>0</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14283,11 +14283,11 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15099,11 +15099,11 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15405,7 +15405,7 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>25022</v>
+        <v>0</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>982</v>
+        <v>0</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>26312</v>
+        <v>0</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17853,11 +17853,11 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17887,11 +17887,11 @@
         <v>1</v>
       </c>
       <c r="G505" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17921,11 +17921,11 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17955,11 +17955,11 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>0</v>
+        <v>9414</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19995,7 +19995,7 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>0</v>
+        <v>29593</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         <v>1</v>
       </c>
       <c r="G637" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22783,11 +22783,11 @@
         <v>1</v>
       </c>
       <c r="G649" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>11063</v>
+        <v>0</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>0</v>
+        <v>1184</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>30616</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23973,7 +23973,7 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
@@ -24313,11 +24313,11 @@
         <v>1</v>
       </c>
       <c r="G694" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24347,11 +24347,11 @@
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24381,11 +24381,11 @@
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24449,11 +24449,11 @@
         <v>1</v>
       </c>
       <c r="G698" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24483,11 +24483,11 @@
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25061,11 @@
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25095,11 +25095,11 @@
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -25503,11 +25503,11 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25537,11 +25537,11 @@
         <v>1</v>
       </c>
       <c r="G730" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25571,11 +25571,11 @@
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26285,11 +26285,11 @@
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26319,11 +26319,11 @@
         <v>1</v>
       </c>
       <c r="G753" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>0</v>
+        <v>26935</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27339,11 +27339,11 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27373,11 +27373,11 @@
         <v>1</v>
       </c>
       <c r="G784" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27407,11 +27407,11 @@
         <v>1</v>
       </c>
       <c r="G785" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27441,11 +27441,11 @@
         <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27509,11 +27509,11 @@
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27543,11 +27543,11 @@
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27679,11 +27679,11 @@
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27713,11 +27713,11 @@
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27747,11 +27747,11 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27815,11 +27815,11 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
@@ -28495,11 +28495,11 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28869,11 +28869,11 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29481,11 +29481,11 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29515,11 +29515,11 @@
         <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29549,11 +29549,11 @@
         <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -29923,11 +29923,11 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>21448</v>
+        <v>0</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29957,11 +29957,11 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29991,11 +29991,11 @@
         <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30025,11 +30025,11 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30093,11 +30093,11 @@
         <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30127,11 +30127,11 @@
         <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30161,11 +30161,11 @@
         <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30195,11 +30195,11 @@
         <v>1</v>
       </c>
       <c r="G867" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30263,11 +30263,11 @@
         <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>972</v>
+        <v>0</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30297,11 +30297,11 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30501,11 +30501,11 @@
         <v>1</v>
       </c>
       <c r="G876" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30569,11 +30569,11 @@
         <v>1</v>
       </c>
       <c r="G878" t="n">
-        <v>0</v>
+        <v>998</v>
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30603,11 +30603,11 @@
         <v>1</v>
       </c>
       <c r="G879" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30637,11 +30637,11 @@
         <v>1</v>
       </c>
       <c r="G880" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30671,11 +30671,11 @@
         <v>1</v>
       </c>
       <c r="G881" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30705,11 +30705,11 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>0</v>
+        <v>6839</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31011,7 +31011,7 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>28131</v>
+        <v>0</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8233</v>
+        <v>7680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>349cb152897646c5001440f4a2229504daee8898f5bfef793234e313b4c20e6b</t>
+          <t>421526a9ce695ef3e5c688ce2541e0db62f06e10f680ab1f016df935c3c8cc9c</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4816</v>
+        <v>5074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>260427654b84f7eab8a27e86bca3cf12fc8fe54047b9c8dcbd6d914e6befcc8a</t>
+          <t>0fa177f6fe7e8730a52a8c615647bccba9ee1396f716e8a1325d9a3f811c6a9d</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>285711</v>
+        <v>289688</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>f726e0fa5fc4e02eaca559cf6e4c6f44e6468abe52e53734e819afeac09f7258</t>
+          <t>db134c0627367831d5b277d8a0b91a437a413c65e207eeadea52b4de0833e9ac</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33129</v>
+        <v>33126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>314764c1cdf5d0070d5a8cff529e7c2c91c17aabc4148fc4ac72af6a521e2292</t>
+          <t>827f226c34e8570ffb8d11fee8fe7b0af2b3182496f1cd5dcc8d8c91eb520b43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4338</v>
+        <v>4558</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60dec5766018abb9b617a4e4630a67b41a59d533e77392a91264202fc11e0a1e</t>
+          <t>1930da89cd2b5a5a96884f9a477c688d4050827a2b9af5d585b63e4b087577ad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>612</v>
+        <v>497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>493022c1084871c64a1193d45deaaccd44522cbc46df77110adef602a273792d</t>
+          <t>d2a566e9ee6ab502dee18ac2d5ffae2b60e12d12f71520d7b25e9a99a3cd9ea3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>03b6373a65c114d64165ecf22b53854506fedf9065b816763f4cb2d1bfbea18a</t>
+          <t>e31164e9bedc47541f8fe27b292e8ccbd7e566bb7f3abd7bbfff545656955705</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1143</v>
+        <v>1209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>b34534c0a9f1fe02db0d24e3adcdfed0ec4ee76f945aafa09760f4c60afd7616</t>
+          <t>07f9d4dc49602546fcf47eb4ebacb5c4ea32498e952f278f614cb84830629b94</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>640</v>
+        <v>573</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>815c356689b4f7c995e4caeac2601dd06ee173db8b82c988e348acfa17876f9a</t>
+          <t>6b551336a862e753fdeea8dc737f854837d3fbf304480cb000ca59f0c79928c6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7680</v>
+        <v>8664</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5074</v>
+        <v>5593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>289688</v>
+        <v>345275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33126</v>
+        <v>36347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4558</v>
+        <v>5149</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>497</v>
+        <v>812</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>330</v>
+        <v>286</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1209</v>
+        <v>1196</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>22276</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>25483</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>9131</v>
+        <v>0</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>1449</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>22532</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14283,11 +14283,11 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14351,11 +14351,11 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14385,11 +14385,11 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14453,11 +14453,11 @@
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15099,11 +15099,11 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15405,7 +15405,7 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>25022</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>9414</v>
+        <v>0</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>968</v>
+        <v>0</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,7 +19995,7 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>23116</v>
+        <v>0</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20913,7 +20913,7 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22783,11 +22783,11 @@
         <v>1</v>
       </c>
       <c r="G649" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>11063</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>1184</v>
+        <v>0</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25061,11 @@
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25095,11 +25095,11 @@
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -25605,11 +25605,11 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26523,11 +26523,11 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>26935</v>
+        <v>0</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27033,7 +27033,7 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27339,11 +27339,11 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27679,11 +27679,11 @@
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27713,11 +27713,11 @@
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27747,11 +27747,11 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27815,11 +27815,11 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>811</v>
+        <v>0</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>24933</v>
+        <v>0</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28427,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="G816" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28869,11 +28869,11 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29175,11 +29175,11 @@
         <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29209,11 +29209,11 @@
         <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29243,11 +29243,11 @@
         <v>1</v>
       </c>
       <c r="G839" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29277,11 +29277,11 @@
         <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29481,7 +29481,7 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
@@ -29923,11 +29923,11 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>0</v>
+        <v>21448</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29957,11 +29957,11 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29991,11 +29991,11 @@
         <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30025,11 +30025,11 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>6839</v>
+        <v>0</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31011,11 +31011,11 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31045,11 +31045,11 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31079,11 +31079,11 @@
         <v>1</v>
       </c>
       <c r="G893" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31113,11 +31113,11 @@
         <v>1</v>
       </c>
       <c r="G894" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31181,11 +31181,11 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31317,7 +31317,7 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>0</v>
+        <v>28131</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31521,11 +31521,11 @@
         <v>1</v>
       </c>
       <c r="G906" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31555,11 +31555,11 @@
         <v>1</v>
       </c>
       <c r="G907" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31623,11 +31623,11 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31657,11 +31657,11 @@
         <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7680</v>
+        <v>8664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>421526a9ce695ef3e5c688ce2541e0db62f06e10f680ab1f016df935c3c8cc9c</t>
+          <t>800ebd0d67d39b523467c8ea7f68c4e3c2229ca495bbd032d032731b803f85dd</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5074</v>
+        <v>5593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0fa177f6fe7e8730a52a8c615647bccba9ee1396f716e8a1325d9a3f811c6a9d</t>
+          <t>ded9cea930ea8486ad8a697bd1a5987793255f7425b978b729ed388577e8d5f4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>289688</v>
+        <v>345275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>db134c0627367831d5b277d8a0b91a437a413c65e207eeadea52b4de0833e9ac</t>
+          <t>92fe5ae834362eddcd34680c1bd65595302ed952fa73a562fb9aa6590d4a1a00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33126</v>
+        <v>36347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>827f226c34e8570ffb8d11fee8fe7b0af2b3182496f1cd5dcc8d8c91eb520b43</t>
+          <t>7593a347b043c3072caaac57dff374ced0f9be7b4756315ef1aeb2eaae805d5a</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4558</v>
+        <v>5149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1930da89cd2b5a5a96884f9a477c688d4050827a2b9af5d585b63e4b087577ad</t>
+          <t>8df2e12ad1369be77905aa94606f4857a56a566413b6deafdd2a58915c80a010</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>497</v>
+        <v>812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>d2a566e9ee6ab502dee18ac2d5ffae2b60e12d12f71520d7b25e9a99a3cd9ea3</t>
+          <t>020f127285d1bcae04d3e1e4b4146b78de6d880a79db0a94478c423067d02b61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>330</v>
+        <v>286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>e31164e9bedc47541f8fe27b292e8ccbd7e566bb7f3abd7bbfff545656955705</t>
+          <t>350ef1f4120a01a0578710c9084c632154368023eabf3fec5ceab1e9b0f05c68</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1209</v>
+        <v>1196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>07f9d4dc49602546fcf47eb4ebacb5c4ea32498e952f278f614cb84830629b94</t>
+          <t>f52cd61ae6368202127653a2a2c27a6a2b8c9a239e36d4c9256d031b7ded52a4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6b551336a862e753fdeea8dc737f854837d3fbf304480cb000ca59f0c79928c6</t>
+          <t>8574cb13fa5e37f85bd8c789ef297c3791045d2212dd583b822101e509916437</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8664</v>
+        <v>7651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5593</v>
+        <v>4760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>345275</v>
+        <v>195026</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36347</v>
+        <v>27257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5149</v>
+        <v>4019</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>812</v>
+        <v>362</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>286</v>
+        <v>198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1196</v>
+        <v>1056</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>585</v>
+        <v>536</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>20663</v>
+        <v>0</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>524</v>
+        <v>0</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6599,11 +6599,11 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>28324</v>
+        <v>0</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>9347</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>981</v>
+        <v>0</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>25483</v>
+        <v>0</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12957,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13875,7 +13875,7 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14283,11 +14283,11 @@
         <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14351,11 +14351,11 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14385,11 +14385,11 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>29916</v>
+        <v>0</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>25022</v>
+        <v>0</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,7 +17241,7 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>982</v>
+        <v>0</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>28253</v>
+        <v>0</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,7 +19995,7 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
@@ -20199,11 +20199,11 @@
         <v>1</v>
       </c>
       <c r="G573" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20913,7 +20913,7 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21831,11 +21831,11 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22749,7 +22749,7 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>11063</v>
+        <v>0</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>0</v>
+        <v>1184</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25061,11 @@
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25095,11 +25095,11 @@
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -25605,11 +25605,11 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26115,7 +26115,7 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
@@ -26523,11 +26523,11 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>0</v>
+        <v>26935</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27033,7 +27033,7 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27339,11 +27339,11 @@
         <v>1</v>
       </c>
       <c r="G783" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27679,11 +27679,11 @@
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27713,11 +27713,11 @@
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27747,11 +27747,11 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27815,11 +27815,11 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>0</v>
+        <v>24933</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28427,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="G816" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28869,11 +28869,11 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29175,11 +29175,11 @@
         <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29209,11 +29209,11 @@
         <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29243,11 +29243,11 @@
         <v>1</v>
       </c>
       <c r="G839" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29277,11 +29277,11 @@
         <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29481,7 +29481,7 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
@@ -29923,11 +29923,11 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>21448</v>
+        <v>0</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29957,11 +29957,11 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29991,11 +29991,11 @@
         <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30025,11 +30025,11 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>0</v>
+        <v>6839</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31011,11 +31011,11 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31045,11 +31045,11 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31079,11 +31079,11 @@
         <v>1</v>
       </c>
       <c r="G893" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31113,11 +31113,11 @@
         <v>1</v>
       </c>
       <c r="G894" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31181,11 +31181,11 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31317,7 +31317,7 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>28131</v>
+        <v>0</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31521,11 +31521,11 @@
         <v>1</v>
       </c>
       <c r="G906" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31555,11 +31555,11 @@
         <v>1</v>
       </c>
       <c r="G907" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31623,11 +31623,11 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31657,11 +31657,11 @@
         <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8664</v>
+        <v>7651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>800ebd0d67d39b523467c8ea7f68c4e3c2229ca495bbd032d032731b803f85dd</t>
+          <t>71e05064eb32ff1c982b3f8a9402142ba46df28b837923f555cd6e240da3e6a0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5593</v>
+        <v>4760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ded9cea930ea8486ad8a697bd1a5987793255f7425b978b729ed388577e8d5f4</t>
+          <t>45b34def867adfeb2dd6104009c5891885910418d3e9514bf9040f8da7af9e39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>345275</v>
+        <v>195026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>92fe5ae834362eddcd34680c1bd65595302ed952fa73a562fb9aa6590d4a1a00</t>
+          <t>017262e5fb12ae37da1364528da8e18f6f050ba4244d25f364480a0d02522313</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36347</v>
+        <v>27257</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7593a347b043c3072caaac57dff374ced0f9be7b4756315ef1aeb2eaae805d5a</t>
+          <t>ad60dc81328e149d37fdb34f4730f800d15bac1517934ce4b43681ef5957941e</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5149</v>
+        <v>4019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8df2e12ad1369be77905aa94606f4857a56a566413b6deafdd2a58915c80a010</t>
+          <t>c9cc8ea8a679797ef95659b42114061a75385113d62ac09e799fce6c4da4c972</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>812</v>
+        <v>362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>020f127285d1bcae04d3e1e4b4146b78de6d880a79db0a94478c423067d02b61</t>
+          <t>355bfbf7d3b3a50543828115d0058f08ea02e6b459cbb67f097e364077eb10a0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>286</v>
+        <v>198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>350ef1f4120a01a0578710c9084c632154368023eabf3fec5ceab1e9b0f05c68</t>
+          <t>9d712fe2f067bc9c828254819213190ec1019ca9aea2fd55e6108d763df78f2d</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1196</v>
+        <v>1056</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>f52cd61ae6368202127653a2a2c27a6a2b8c9a239e36d4c9256d031b7ded52a4</t>
+          <t>4ad002576e293d45de1a992f54acf60cdc0386eff9c48401ba00ed9b78c46ce2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>585</v>
+        <v>536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8574cb13fa5e37f85bd8c789ef297c3791045d2212dd583b822101e509916437</t>
+          <t>8972cc8c9e4f46538b4f866c6d0ffc6bb07a683dd258d77792e9bd603f3682cc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7651</v>
+        <v>8029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4760</v>
+        <v>4854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>195026</v>
+        <v>321559</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27257</v>
+        <v>34705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4019</v>
+        <v>4859</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>362</v>
+        <v>625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>198</v>
+        <v>308</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1056</v>
+        <v>1205</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>536</v>
+        <v>604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>20663</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>28324</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>9347</v>
+        <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>1449</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12957,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>22532</v>
+        <v>0</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13875,7 +13875,7 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -14453,11 +14453,11 @@
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14521,11 +14521,11 @@
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14555,11 +14555,11 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>29916</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15099,11 +15099,11 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="G428" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15303,11 +15303,11 @@
         <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>0</v>
+        <v>1116</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>25022</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0</v>
+        <v>26312</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,11 +17853,11 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17887,11 +17887,11 @@
         <v>1</v>
       </c>
       <c r="G505" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17921,11 +17921,11 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17955,11 +17955,11 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,7 +20913,7 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
@@ -21831,11 +21831,11 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>11063</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23361,7 +23361,7 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>30616</v>
+        <v>0</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24313,11 +24313,11 @@
         <v>1</v>
       </c>
       <c r="G694" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24347,11 +24347,11 @@
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24381,11 +24381,11 @@
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24449,11 +24449,11 @@
         <v>1</v>
       </c>
       <c r="G698" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24483,11 +24483,11 @@
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>617</v>
+        <v>0</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25061,11 @@
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25095,11 +25095,11 @@
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -25605,11 +25605,11 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25673,11 +25673,11 @@
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26285,11 +26285,11 @@
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>496</v>
+        <v>0</v>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26319,11 +26319,11 @@
         <v>1</v>
       </c>
       <c r="G753" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27645,7 +27645,7 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>24933</v>
+        <v>0</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28427,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="G816" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28869,11 +28869,11 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29515,11 +29515,11 @@
         <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29549,11 +29549,11 @@
         <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29787,11 +29787,11 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29821,11 +29821,11 @@
         <v>1</v>
       </c>
       <c r="G856" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29855,11 +29855,11 @@
         <v>1</v>
       </c>
       <c r="G857" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29889,11 +29889,11 @@
         <v>1</v>
       </c>
       <c r="G858" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30093,11 +30093,11 @@
         <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30127,11 +30127,11 @@
         <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30161,11 +30161,11 @@
         <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30195,11 +30195,11 @@
         <v>1</v>
       </c>
       <c r="G867" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30263,11 +30263,11 @@
         <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>0</v>
+        <v>972</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30297,11 +30297,11 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>6839</v>
+        <v>0</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31011,11 +31011,11 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31045,11 +31045,11 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31079,11 +31079,11 @@
         <v>1</v>
       </c>
       <c r="G893" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31113,11 +31113,11 @@
         <v>1</v>
       </c>
       <c r="G894" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31181,11 +31181,11 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31317,7 +31317,7 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>0</v>
+        <v>28131</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31521,11 +31521,11 @@
         <v>1</v>
       </c>
       <c r="G906" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31555,11 +31555,11 @@
         <v>1</v>
       </c>
       <c r="G907" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31623,11 +31623,11 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31657,11 +31657,11 @@
         <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7651</v>
+        <v>8029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71e05064eb32ff1c982b3f8a9402142ba46df28b837923f555cd6e240da3e6a0</t>
+          <t>a5015af4f749125fc6abd968341b90edb5cde8195315cfb6c129f540a5fb4cfa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4760</v>
+        <v>4854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>45b34def867adfeb2dd6104009c5891885910418d3e9514bf9040f8da7af9e39</t>
+          <t>07d5f0ef493617bdf9db8ee4f161aa5447c7b29416d8fef93338d34ba98a1ee0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>195026</v>
+        <v>321559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>017262e5fb12ae37da1364528da8e18f6f050ba4244d25f364480a0d02522313</t>
+          <t>6a3091c769cbfcac20788cdc6654233f4fcca452faa71a27143b94ec156f1c0a</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27257</v>
+        <v>34705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ad60dc81328e149d37fdb34f4730f800d15bac1517934ce4b43681ef5957941e</t>
+          <t>5e213e35eb0a599c42848aca0afdb7ea335bbfa967a61fa1592e8d0b4c19b25d</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4019</v>
+        <v>4859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>c9cc8ea8a679797ef95659b42114061a75385113d62ac09e799fce6c4da4c972</t>
+          <t>600dd7c7e77798bf157334e97b41c0218261a393f52fdedb85deee3442667a20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>362</v>
+        <v>625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>355bfbf7d3b3a50543828115d0058f08ea02e6b459cbb67f097e364077eb10a0</t>
+          <t>7d1ef8f34df1d8b31bb4a660c35b6584d8140f624f67542a07a246d4d9e42193</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>198</v>
+        <v>308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9d712fe2f067bc9c828254819213190ec1019ca9aea2fd55e6108d763df78f2d</t>
+          <t>cbd7edf4c4e05d06adc3428bcdbefb86681f159a2dc10a7482407daf9bb8c802</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1056</v>
+        <v>1205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4ad002576e293d45de1a992f54acf60cdc0386eff9c48401ba00ed9b78c46ce2</t>
+          <t>b37500bc56ed658fe5f91cd27e200f9aa5c5b646e479e3f5983b6e9ac2b5aba9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>536</v>
+        <v>604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8972cc8c9e4f46538b4f866c6d0ffc6bb07a683dd258d77792e9bd603f3682cc</t>
+          <t>4683f9d377a03c934af431430135ef82fb4b062c098373b1735e24dae9ea3af5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8029</v>
+        <v>6773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4854</v>
+        <v>4045</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>321559</v>
+        <v>209928</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34705</v>
+        <v>29152</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4859</v>
+        <v>4134</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>625</v>
+        <v>460</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1205</v>
+        <v>1121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>604</v>
+        <v>508</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>22276</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6599,11 +6599,11 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>28324</v>
+        <v>0</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>9347</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>0</v>
+        <v>9131</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12651,7 +12651,7 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>25022</v>
+        <v>0</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>982</v>
+        <v>0</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>26312</v>
+        <v>0</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>28253</v>
+        <v>0</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>23116</v>
+        <v>0</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20913,7 +20913,7 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>11063</v>
+        <v>0</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23361,7 +23361,7 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>30616</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24313,11 +24313,11 @@
         <v>1</v>
       </c>
       <c r="G694" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24347,11 +24347,11 @@
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24381,11 +24381,11 @@
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24449,11 +24449,11 @@
         <v>1</v>
       </c>
       <c r="G698" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24483,11 +24483,11 @@
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,7 +24585,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25061,11 @@
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25095,11 +25095,11 @@
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -25537,11 +25537,11 @@
         <v>1</v>
       </c>
       <c r="G730" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25571,11 +25571,11 @@
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25605,11 +25605,11 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25673,11 +25673,11 @@
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26285,11 +26285,11 @@
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26319,11 +26319,11 @@
         <v>1</v>
       </c>
       <c r="G753" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27373,11 +27373,11 @@
         <v>1</v>
       </c>
       <c r="G784" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27407,11 +27407,11 @@
         <v>1</v>
       </c>
       <c r="G785" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27441,11 +27441,11 @@
         <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27509,11 +27509,11 @@
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27543,11 +27543,11 @@
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27645,7 +27645,7 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>0</v>
+        <v>24933</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -29515,11 +29515,11 @@
         <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29549,11 +29549,11 @@
         <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29787,11 +29787,11 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30093,11 +30093,11 @@
         <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30127,11 +30127,11 @@
         <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30161,11 +30161,11 @@
         <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30195,11 +30195,11 @@
         <v>1</v>
       </c>
       <c r="G867" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30263,11 +30263,11 @@
         <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>972</v>
+        <v>0</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30297,11 +30297,11 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30399,7 +30399,7 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>0</v>
+        <v>6839</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31011,11 +31011,11 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31045,11 +31045,11 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31079,11 +31079,11 @@
         <v>1</v>
       </c>
       <c r="G893" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31113,11 +31113,11 @@
         <v>1</v>
       </c>
       <c r="G894" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31181,11 +31181,11 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31317,11 +31317,11 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31351,11 +31351,11 @@
         <v>1</v>
       </c>
       <c r="G901" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>28131</v>
+        <v>0</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31521,11 +31521,11 @@
         <v>1</v>
       </c>
       <c r="G906" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31555,11 +31555,11 @@
         <v>1</v>
       </c>
       <c r="G907" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31623,11 +31623,11 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31657,11 +31657,11 @@
         <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8029</v>
+        <v>6773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>a5015af4f749125fc6abd968341b90edb5cde8195315cfb6c129f540a5fb4cfa</t>
+          <t>8763fe9a474bca63013500461d0768ce57620adbefac49a2dbdc342fd1213814</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4854</v>
+        <v>4045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>07d5f0ef493617bdf9db8ee4f161aa5447c7b29416d8fef93338d34ba98a1ee0</t>
+          <t>ddc75cf70201f7eae7224312ef76ac5a98478a34bd8cc53478faa4729c5efaa3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>321559</v>
+        <v>209928</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6a3091c769cbfcac20788cdc6654233f4fcca452faa71a27143b94ec156f1c0a</t>
+          <t>848d7c0cbb299fbd55c6e3a27cb74abd4d7a34b18755b02ba8cf460a73efa945</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34705</v>
+        <v>29152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5e213e35eb0a599c42848aca0afdb7ea335bbfa967a61fa1592e8d0b4c19b25d</t>
+          <t>eb537574c1bfbf3c72dad2c0ffdc465ee327e0eb18d24434a9fc02c299b78a40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4859</v>
+        <v>4134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>600dd7c7e77798bf157334e97b41c0218261a393f52fdedb85deee3442667a20</t>
+          <t>b9aed1704da760d30c7d47233f7be9913c77ebb13ea3cf91df350581d7195e2d</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>625</v>
+        <v>460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7d1ef8f34df1d8b31bb4a660c35b6584d8140f624f67542a07a246d4d9e42193</t>
+          <t>e36f55ecfc1081c0a521ca5784abb67f0edbacc6b2429f418a99a7c3b46419a8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cbd7edf4c4e05d06adc3428bcdbefb86681f159a2dc10a7482407daf9bb8c802</t>
+          <t>6a12bbddf0d309c30ed64c1e2f8f08d0b362a5e4caa524fe2d1c0158b2a315b5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1205</v>
+        <v>1121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>b37500bc56ed658fe5f91cd27e200f9aa5c5b646e479e3f5983b6e9ac2b5aba9</t>
+          <t>a293c9e31b126182b16934f265f7812c73ccd47a514ac347a3e70a1b79873e34</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>604</v>
+        <v>508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4683f9d377a03c934af431430135ef82fb4b062c098373b1735e24dae9ea3af5</t>
+          <t>fd0988c81a80c4ff2c73e58a82377ce48cdf79ebfbaf5d7814a0e446f06ebd1e</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6773</v>
+        <v>8091</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4045</v>
+        <v>5803</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>209928</v>
+        <v>288134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29152</v>
+        <v>38499</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4134</v>
+        <v>5166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>460</v>
+        <v>633</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1121</v>
+        <v>1274</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>508</v>
+        <v>705</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,11 +1839,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>9019</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>20663</v>
+        <v>0</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>524</v>
+        <v>0</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6089,11 +6089,11 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6123,11 +6123,11 @@
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>25483</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>22532</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>25022</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>0</v>
+        <v>9414</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>968</v>
+        <v>0</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19995,7 +19995,7 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20199,11 +20199,11 @@
         <v>1</v>
       </c>
       <c r="G573" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>734</v>
+        <v>0</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>29593</v>
+        <v>0</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>536</v>
+        <v>0</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         <v>1</v>
       </c>
       <c r="G637" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22443,7 +22443,7 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>11063</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23225,11 +23225,11 @@
         <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>1184</v>
+        <v>0</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24585,7 +24585,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
@@ -25231,11 +25231,11 @@
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25265,11 +25265,11 @@
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25299,11 +25299,11 @@
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25333,11 +25333,11 @@
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>21955</v>
+        <v>0</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25367,11 +25367,11 @@
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25401,11 +25401,11 @@
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25503,11 +25503,11 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,7 +26115,7 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
@@ -26285,11 +26285,11 @@
         <v>1</v>
       </c>
       <c r="G752" t="n">
-        <v>496</v>
+        <v>0</v>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26319,11 +26319,11 @@
         <v>1</v>
       </c>
       <c r="G753" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26421,11 +26421,11 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26455,11 +26455,11 @@
         <v>1</v>
       </c>
       <c r="G757" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26489,11 +26489,11 @@
         <v>1</v>
       </c>
       <c r="G758" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26523,11 +26523,11 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26727,7 +26727,7 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27373,11 +27373,11 @@
         <v>1</v>
       </c>
       <c r="G784" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27407,11 +27407,11 @@
         <v>1</v>
       </c>
       <c r="G785" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27441,11 +27441,11 @@
         <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27509,11 +27509,11 @@
         <v>1</v>
       </c>
       <c r="G788" t="n">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27543,11 +27543,11 @@
         <v>1</v>
       </c>
       <c r="G789" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27645,7 +27645,7 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
@@ -28155,11 +28155,11 @@
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28223,11 +28223,11 @@
         <v>1</v>
       </c>
       <c r="G809" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28257,11 +28257,11 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>24933</v>
+        <v>0</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28733,11 +28733,11 @@
         <v>1</v>
       </c>
       <c r="G824" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28767,11 +28767,11 @@
         <v>1</v>
       </c>
       <c r="G825" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -29277,11 +29277,11 @@
         <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29481,11 +29481,11 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29515,11 +29515,11 @@
         <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29549,11 +29549,11 @@
         <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -29821,11 +29821,11 @@
         <v>1</v>
       </c>
       <c r="G856" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29855,11 +29855,11 @@
         <v>1</v>
       </c>
       <c r="G857" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29889,11 +29889,11 @@
         <v>1</v>
       </c>
       <c r="G858" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29923,11 +29923,11 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>0</v>
+        <v>21448</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29957,11 +29957,11 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29991,11 +29991,11 @@
         <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30025,11 +30025,11 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30093,11 +30093,11 @@
         <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30127,11 +30127,11 @@
         <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30161,11 +30161,11 @@
         <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30195,11 +30195,11 @@
         <v>1</v>
       </c>
       <c r="G867" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30263,11 +30263,11 @@
         <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>0</v>
+        <v>972</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30297,11 +30297,11 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30433,11 +30433,11 @@
         <v>1</v>
       </c>
       <c r="G874" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30467,11 +30467,11 @@
         <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30501,11 +30501,11 @@
         <v>1</v>
       </c>
       <c r="G876" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30569,11 +30569,11 @@
         <v>1</v>
       </c>
       <c r="G878" t="n">
-        <v>998</v>
+        <v>0</v>
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30603,11 +30603,11 @@
         <v>1</v>
       </c>
       <c r="G879" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30637,11 +30637,11 @@
         <v>1</v>
       </c>
       <c r="G880" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30671,11 +30671,11 @@
         <v>1</v>
       </c>
       <c r="G881" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30705,7 +30705,7 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
@@ -31623,11 +31623,11 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31657,11 +31657,11 @@
         <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6773</v>
+        <v>8091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8763fe9a474bca63013500461d0768ce57620adbefac49a2dbdc342fd1213814</t>
+          <t>7a0c19e997e5956e7a2f23b99c59382667ab208457a4cf202592050f51c6bd59</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4045</v>
+        <v>5803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ddc75cf70201f7eae7224312ef76ac5a98478a34bd8cc53478faa4729c5efaa3</t>
+          <t>d0a5b475cc77dd990c0710b50ddbc378540c9e7a5f4fdec7f71e671a8cf808db</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>209928</v>
+        <v>288134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>848d7c0cbb299fbd55c6e3a27cb74abd4d7a34b18755b02ba8cf460a73efa945</t>
+          <t>7d3f7591cc8da0007a91fe827a5bc9bfc047463adb83dce1c597498d01390fa9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29152</v>
+        <v>38499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>eb537574c1bfbf3c72dad2c0ffdc465ee327e0eb18d24434a9fc02c299b78a40</t>
+          <t>4b85d6ef6a19233a95fb58b9aac44853576125bddd8fc862e1115c1f04c46f6b</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4134</v>
+        <v>5166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>b9aed1704da760d30c7d47233f7be9913c77ebb13ea3cf91df350581d7195e2d</t>
+          <t>7e8973ffd7e6bd49ddc260be3f514f565ed78936dddbd725a81390ae3964bd70</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>460</v>
+        <v>633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>e36f55ecfc1081c0a521ca5784abb67f0edbacc6b2429f418a99a7c3b46419a8</t>
+          <t>ba5ddff152f21c9f1c2064ccf55ac95938307912c0b49c2f37ec433ebdaca7f2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6a12bbddf0d309c30ed64c1e2f8f08d0b362a5e4caa524fe2d1c0158b2a315b5</t>
+          <t>852f093bab0f1492e4a7ed9352b57e57aa08127264125d1d53df0dfb5f5783d7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1121</v>
+        <v>1274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>a293c9e31b126182b16934f265f7812c73ccd47a514ac347a3e70a1b79873e34</t>
+          <t>aa1395efae65e79c16efd406b80569281bba577d872732c85b5b58f438e7d8b3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>508</v>
+        <v>705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>fd0988c81a80c4ff2c73e58a82377ce48cdf79ebfbaf5d7814a0e446f06ebd1e</t>
+          <t>f6928dcc20ed1f0f056f460a34466ca46243a0f450e44d8c8cb5b49f51b88e70</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8091</v>
+        <v>8761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5803</v>
+        <v>6027</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>288134</v>
+        <v>418161</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38499</v>
+        <v>37428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5166</v>
+        <v>5219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242</v>
+        <v>374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1274</v>
+        <v>1318</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>705</v>
+        <v>653</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>22276</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>20663</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6599,11 +6599,11 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>28324</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9897,7 +9897,7 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15405,7 +15405,7 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0</v>
+        <v>26312</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>9414</v>
+        <v>0</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20199,11 +20199,11 @@
         <v>1</v>
       </c>
       <c r="G573" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20301,7 +20301,7 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,7 +21219,7 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>0</v>
+        <v>29593</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         <v>1</v>
       </c>
       <c r="G637" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22443,7 +22443,7 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22783,11 +22783,11 @@
         <v>1</v>
       </c>
       <c r="G649" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23055,7 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
@@ -23259,11 +23259,11 @@
         <v>1</v>
       </c>
       <c r="G663" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23293,11 +23293,11 @@
         <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>0</v>
+        <v>1184</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24313,11 +24313,11 @@
         <v>1</v>
       </c>
       <c r="G694" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24347,11 +24347,11 @@
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24381,11 +24381,11 @@
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24449,11 +24449,11 @@
         <v>1</v>
       </c>
       <c r="G698" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24483,11 +24483,11 @@
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24585,7 +24585,7 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25061,11 @@
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25095,11 +25095,11 @@
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25197,11 +25197,11 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25503,11 +25503,11 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25537,11 +25537,11 @@
         <v>1</v>
       </c>
       <c r="G730" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25571,11 +25571,11 @@
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25605,11 +25605,11 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25673,11 +25673,11 @@
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25809,7 +25809,7 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26421,11 +26421,11 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26455,11 +26455,11 @@
         <v>1</v>
       </c>
       <c r="G757" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26489,11 +26489,11 @@
         <v>1</v>
       </c>
       <c r="G758" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26523,11 +26523,11 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26727,7 +26727,7 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27645,7 +27645,7 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
@@ -28155,11 +28155,11 @@
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28223,11 +28223,11 @@
         <v>1</v>
       </c>
       <c r="G809" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28257,11 +28257,11 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28733,11 +28733,11 @@
         <v>1</v>
       </c>
       <c r="G824" t="n">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28767,11 +28767,11 @@
         <v>1</v>
       </c>
       <c r="G825" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -29277,11 +29277,11 @@
         <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30433,11 +30433,11 @@
         <v>1</v>
       </c>
       <c r="G874" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30467,11 +30467,11 @@
         <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30501,11 +30501,11 @@
         <v>1</v>
       </c>
       <c r="G876" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30705,11 +30705,11 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>6839</v>
+        <v>0</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31011,7 +31011,7 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
@@ -31317,11 +31317,11 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31351,11 +31351,11 @@
         <v>1</v>
       </c>
       <c r="G901" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>0</v>
+        <v>28131</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31623,11 +31623,11 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31657,11 +31657,11 @@
         <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31723,11 +31723,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8091</v>
+        <v>8761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7a0c19e997e5956e7a2f23b99c59382667ab208457a4cf202592050f51c6bd59</t>
+          <t>29935bc07de98e38466540ffe8d466432a1b2418250a28f7f5ffc84587fc7257</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31753,11 +31753,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5803</v>
+        <v>6027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>d0a5b475cc77dd990c0710b50ddbc378540c9e7a5f4fdec7f71e671a8cf808db</t>
+          <t>f56fa79aec07541d87966bfa96d9d87e613b414fa1d1b5acd4ac93af358177c2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31783,11 +31783,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>288134</v>
+        <v>418161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7d3f7591cc8da0007a91fe827a5bc9bfc047463adb83dce1c597498d01390fa9</t>
+          <t>1e744428450ce28e953ebc158a79e5e3a40875e9c65a4a7896a913bc6a3fe306</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -31813,11 +31813,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38499</v>
+        <v>37428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4b85d6ef6a19233a95fb58b9aac44853576125bddd8fc862e1115c1f04c46f6b</t>
+          <t>11e5bd59a7ae560c8fa1a0e08775f2297d8163e5a52c6c111406cc5c6195e339</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31843,11 +31843,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5166</v>
+        <v>5219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7e8973ffd7e6bd49ddc260be3f514f565ed78936dddbd725a81390ae3964bd70</t>
+          <t>a7c9964a0b75349fb624abfd75ff714fc73ec559f05ec07ca1eb16165a458eb2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -31873,11 +31873,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ba5ddff152f21c9f1c2064ccf55ac95938307912c0b49c2f37ec433ebdaca7f2</t>
+          <t>666dfa9e2c540c4e0c72f7cd467d56946b623ccf2990b99cc83c4554f2a4db66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31903,11 +31903,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>242</v>
+        <v>374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>852f093bab0f1492e4a7ed9352b57e57aa08127264125d1d53df0dfb5f5783d7</t>
+          <t>f000604545b909a92f56449e41eae2ead44d2f63331584aa6388f0d16c08f8b9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31933,11 +31933,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1274</v>
+        <v>1318</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>aa1395efae65e79c16efd406b80569281bba577d872732c85b5b58f438e7d8b3</t>
+          <t>4383f193202e7599cd6f7d6e7fb7d05034ec7521ede4694f7f20d8a8611d9c74</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31963,11 +31963,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>705</v>
+        <v>653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>f6928dcc20ed1f0f056f460a34466ca46243a0f450e44d8c8cb5b49f51b88e70</t>
+          <t>3c941ad9740344d4495ec3a3da7654edbbed492dbaa71dc359086800d876d67a</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6998</v>
+        <v>8004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3790</v>
+        <v>5077</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>237980</v>
+        <v>246390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25023</v>
+        <v>31068</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3840</v>
+        <v>4204</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>512</v>
+        <v>597</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>938</v>
+        <v>1151</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>417</v>
+        <v>658</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H928"/>
+  <dimension ref="A1:H937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1839,11 +1839,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>20663</v>
+        <v>0</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>524</v>
+        <v>0</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10271,11 +10271,11 @@
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10305,11 +10305,11 @@
         <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10815,11 +10815,11 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10883,11 +10883,11 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10917,11 +10917,11 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10951,11 +10951,11 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>9347</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10985,11 +10985,11 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11019,11 +11019,11 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11053,11 +11053,11 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11121,11 +11121,11 @@
         <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11189,11 +11189,11 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>25483</v>
+        <v>0</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11937,11 +11937,11 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
@@ -12311,11 +12311,11 @@
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>9131</v>
+        <v>0</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12957,11 +12957,11 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12991,11 +12991,11 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13025,11 +13025,11 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>22532</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13127,11 @@
         <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13161,11 +13161,11 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13637,11 +13637,11 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13671,11 +13671,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13739,11 @@
         <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13773,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13875,11 +13875,11 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13943,11 +13943,11 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14181,7 +14181,7 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
@@ -14589,11 +14589,11 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14623,11 +14623,11 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>29916</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14657,11 +14657,11 @@
         <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14725,11 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>1116</v>
+        <v>0</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>25022</v>
+        <v>0</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17649,11 +17649,11 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17683,11 +17683,11 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>26312</v>
+        <v>0</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17717,11 +17717,11 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17751,11 +17751,11 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17785,11 +17785,11 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>28253</v>
+        <v>0</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>23116</v>
+        <v>0</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20913,7 +20913,7 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22137,7 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
@@ -22749,11 +22749,11 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22783,11 +22783,11 @@
         <v>1</v>
       </c>
       <c r="G649" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22817,11 +22817,11 @@
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22851,11 +22851,11 @@
         <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22919,11 +22919,11 @@
         <v>1</v>
       </c>
       <c r="G653" t="n">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22953,11 +22953,11 @@
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22987,11 @@
         <v>1</v>
       </c>
       <c r="G655" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23021,11 +23021,11 @@
         <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23055,11 +23055,11 @@
         <v>1</v>
       </c>
       <c r="G657" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23361,11 +23361,11 @@
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23429,11 +23429,11 @@
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23463,11 @@
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23531,11 @@
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>1184</v>
+        <v>0</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23633,11 +23633,11 @@
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>30616</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23973,11 +23973,11 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24007,11 +24007,11 @@
         <v>1</v>
       </c>
       <c r="G685" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24041,11 +24041,11 @@
         <v>1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24075,11 +24075,11 @@
         <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24143,11 +24143,11 @@
         <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24177,11 +24177,11 @@
         <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24279,7 +24279,7 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24891,11 +24891,11 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24959,11 +24959,11 @@
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24993,11 +24993,11 @@
         <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25061,11 @@
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25095,11 +25095,11 @@
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25163,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25197,11 +25197,11 @@
         <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25231,11 +25231,11 @@
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25265,11 +25265,11 @@
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25299,11 +25299,11 @@
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25333,11 +25333,11 @@
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>0</v>
+        <v>21955</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25367,11 +25367,11 @@
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25401,11 +25401,11 @@
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25503,7 +25503,7 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
@@ -25673,11 +25673,11 @@
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>0</v>
+        <v>26935</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27033,11 +27033,11 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27815,11 +27815,11 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27951,11 +27951,11 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27985,11 +27985,11 @@
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28019,11 +28019,11 @@
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28053,11 +28053,11 @@
         <v>1</v>
       </c>
       <c r="G804" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28121,11 +28121,11 @@
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>0</v>
+        <v>1301</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28155,11 +28155,11 @@
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28223,11 +28223,11 @@
         <v>1</v>
       </c>
       <c r="G809" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28257,11 +28257,11 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>0</v>
+        <v>24933</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28427,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="G816" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28495,11 +28495,11 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28563,7 +28563,7 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29175,11 +29175,11 @@
         <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29209,11 +29209,11 @@
         <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29243,11 +29243,11 @@
         <v>1</v>
       </c>
       <c r="G839" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29277,11 +29277,11 @@
         <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29481,7 +29481,7 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29787,11 +29787,11 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29821,11 +29821,11 @@
         <v>1</v>
       </c>
       <c r="G856" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29855,11 +29855,11 @@
         <v>1</v>
       </c>
       <c r="G857" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29889,11 +29889,11 @@
         <v>1</v>
       </c>
       <c r="G858" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29923,11 +29923,11 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>0</v>
+        <v>21448</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29957,11 +29957,11 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29991,11 +29991,11 @@
         <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30025,11 +30025,11 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30093,11 +30093,11 @@
         <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30127,11 +30127,11 @@
         <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30399,11 +30399,11 @@
         <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30433,11 +30433,11 @@
         <v>1</v>
       </c>
       <c r="G874" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30467,11 +30467,11 @@
         <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30501,11 +30501,11 @@
         <v>1</v>
       </c>
       <c r="G876" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30569,11 +30569,11 @@
         <v>1</v>
       </c>
       <c r="G878" t="n">
-        <v>998</v>
+        <v>0</v>
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30603,11 +30603,11 @@
         <v>1</v>
       </c>
       <c r="G879" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30637,11 +30637,11 @@
         <v>1</v>
       </c>
       <c r="G880" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30705,11 +30705,11 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>0</v>
+        <v>6839</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31011,11 +31011,11 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31045,11 +31045,11 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31079,11 +31079,11 @@
         <v>1</v>
       </c>
       <c r="G893" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31113,11 +31113,11 @@
         <v>1</v>
       </c>
       <c r="G894" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31181,11 +31181,11 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31317,7 +31317,7 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
@@ -31419,11 +31419,11 @@
         <v>1</v>
       </c>
       <c r="G903" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31453,11 +31453,11 @@
         <v>1</v>
       </c>
       <c r="G904" t="n">
-        <v>28131</v>
+        <v>0</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31487,11 +31487,11 @@
         <v>1</v>
       </c>
       <c r="G905" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31521,11 +31521,11 @@
         <v>1</v>
       </c>
       <c r="G906" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31555,11 +31555,11 @@
         <v>1</v>
       </c>
       <c r="G907" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31623,11 +31623,11 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31657,11 +31657,11 @@
         <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31929,11 +31929,11 @@
         <v>1</v>
       </c>
       <c r="G918" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31963,11 +31963,11 @@
         <v>1</v>
       </c>
       <c r="G919" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31997,11 +31997,11 @@
         <v>1</v>
       </c>
       <c r="G920" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -32031,11 +32031,11 @@
         <v>1</v>
       </c>
       <c r="G921" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -32099,11 +32099,11 @@
         <v>1</v>
       </c>
       <c r="G923" t="n">
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -32133,11 +32133,11 @@
         <v>1</v>
       </c>
       <c r="G924" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -32235,11 +32235,11 @@
         <v>1</v>
       </c>
       <c r="G927" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -32269,11 +32269,317 @@
         <v>1</v>
       </c>
       <c r="G928" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B929" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C929" t="n">
+        <v>11391</v>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F929" t="b">
+        <v>1</v>
+      </c>
+      <c r="G929" t="n">
+        <v>82</v>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>race_control</t>
+        </is>
+      </c>
+      <c r="B930" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C930" t="n">
+        <v>11391</v>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F930" t="b">
+        <v>1</v>
+      </c>
+      <c r="G930" t="n">
+        <v>55</v>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B931" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C931" t="n">
+        <v>11391</v>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F931" t="b">
+        <v>1</v>
+      </c>
+      <c r="G931" t="n">
+        <v>0</v>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="B932" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C932" t="n">
+        <v>11391</v>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F932" t="b">
+        <v>1</v>
+      </c>
+      <c r="G932" t="n">
+        <v>620</v>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="B933" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C933" t="n">
+        <v>11391</v>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F933" t="b">
+        <v>1</v>
+      </c>
+      <c r="G933" t="n">
+        <v>92</v>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>pit</t>
+        </is>
+      </c>
+      <c r="B934" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C934" t="n">
+        <v>11391</v>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F934" t="b">
+        <v>0</v>
+      </c>
+      <c r="G934" t="n">
+        <v>0</v>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>skipped_not_applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>starting_grid</t>
+        </is>
+      </c>
+      <c r="B935" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C935" t="n">
+        <v>11391</v>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F935" t="b">
+        <v>1</v>
+      </c>
+      <c r="G935" t="n">
+        <v>0</v>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>drivers</t>
+        </is>
+      </c>
+      <c r="B936" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C936" t="n">
+        <v>11391</v>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F936" t="b">
+        <v>1</v>
+      </c>
+      <c r="G936" t="n">
+        <v>22</v>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>team_radio</t>
+        </is>
+      </c>
+      <c r="B937" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C937" t="n">
+        <v>11391</v>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="F937" t="b">
+        <v>1</v>
+      </c>
+      <c r="G937" t="n">
+        <v>19</v>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -32335,11 +32641,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6998</v>
+        <v>8004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>a103f9b145bd206a45a5d349a0007db0669b6c9c47053188a7443b24854233f4</t>
+          <t>698dda7d5a8c7cf82cc603678b2976d34726bc25b13ec3d97d0eb64b4e792716</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -32365,11 +32671,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3790</v>
+        <v>5077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8425357d2341f1948190c86b5eb9c0ba2cd91b6fadde92c92678a5c39794e979</t>
+          <t>89f9fca578069657346a871f0703611099bcbe189d7720b308936cb8ab21a321</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -32395,11 +32701,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>237980</v>
+        <v>246390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dcf3dcf005358778818fc2eaea2b0d1e364c9a4a0f408f8e0e47ffae0757b67b</t>
+          <t>60d4d3e3d8fa65972b2c90a402a9f7521346d94527537b94f2c5c66cd4000ecf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -32425,11 +32731,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25023</v>
+        <v>31068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ee5d4033afb9a353cba5a52b97b9236efed2c01ab34dac01163e2f8e0674c1a6</t>
+          <t>b060a5e88c1347dc8d720a48deb88955251962ac46a34f5a232041c965ec40c9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -32455,11 +32761,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3840</v>
+        <v>4204</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>65398d843dc47bbc76f37fafaaaeabff0fcb9951112b017f9be15e18be952a16</t>
+          <t>72916118b6d7844213d40fe9c5159c47ac7d2b5ceb559e80d15da73f9ad7bde6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -32485,11 +32791,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>512</v>
+        <v>597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8afe83e02eef53876727e08a96656b731b8120ec86cfc8ff8a0b7bd9cc158615</t>
+          <t>c8dde9e7ab52dd9cea0785b7dde592a80335503d5870274d86aaec05ddd19511</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -32515,11 +32821,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>132</v>
+        <v>220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>daa1f73da2ad2b232d2c1e936cb472f76565917447aebf7420ccec1ff92466ea</t>
+          <t>c0024d58d99ff331d39885c2fb45fac81ab8cf51264c4a24a8da748f87b42fa6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32545,11 +32851,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>938</v>
+        <v>1151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3131e254106faf0726d158130383e6c9aefdd364b69514ef5c79a96b52e5e59f</t>
+          <t>16057aa7c72c838ab97d3a7b6a930bfb6fd9760acf80e19bf8d1019c3580fff8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -32575,11 +32881,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>417</v>
+        <v>658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7de313cd961130fd4bdc92bfc9d2f51d419b68d4a876ce54d528a87ae2eb0bbe</t>
+          <t>3cafb75cee0a32fcd14ef22a14206a8e0de35926d841582469aba803c807d171</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -32604,7 +32910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:P105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39693,6 +39999,74 @@
         <v>1</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>11391</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-10-24T17:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-10-24T18:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1297</v>
+      </c>
+      <c r="G105" t="n">
+        <v>9</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>19</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>-05:00:00</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O105" t="b">
+        <v>0</v>
+      </c>
+      <c r="P105" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8004</v>
+        <v>8406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5077</v>
+        <v>6135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>246390</v>
+        <v>288134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31068</v>
+        <v>36495</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4204</v>
+        <v>4797</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1151</v>
+        <v>1306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>658</v>
+        <v>739</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H937"/>
+  <dimension ref="A1:H946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>22276</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>9019</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5783,11 +5783,11 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5817,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6089,11 +6089,11 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6123,11 +6123,11 @@
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -6599,11 +6599,11 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7449,11 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9285,11 +9285,11 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -11223,11 +11223,11 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11291,11 +11291,11 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11325,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11393,11 +11393,11 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>25483</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12039,11 +12039,11 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12107,11 +12107,11 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12209,11 +12209,11 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12243,11 +12243,11 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12277,11 +12277,11 @@
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>0</v>
+        <v>9131</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12515,11 +12515,11 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12549,11 +12549,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12583,11 +12583,11 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12651,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12685,11 @@
         <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12719,11 +12719,11 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12753,11 +12753,11 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12821,11 +12821,11 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>1449</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12855,11 +12855,11 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12923,11 +12923,11 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12957,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14181,7 +14181,7 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
@@ -14793,11 +14793,11 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14827,11 +14827,11 @@
         <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14861,11 +14861,11 @@
         <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14895,11 +14895,11 @@
         <v>1</v>
       </c>
       <c r="G417" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14963,11 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14997,11 +14997,11 @@
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15405,7 +15405,7 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>0</v>
+        <v>1116</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16017,11 +16017,11 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16051,11 +16051,11 @@
         <v>1</v>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16085,11 +16085,11 @@
         <v>1</v>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16119,11 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v>1</v>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
+        <v>25022</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         <v>1</v>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17241,11 +17241,11 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17275,11 +17275,11 @@
         <v>1</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17343,11 +17343,11 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18465,11 +18465,11 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18499,11 +18499,11 @@
         <v>1</v>
       </c>
       <c r="G523" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18533,11 +18533,11 @@
         <v>1</v>
       </c>
       <c r="G524" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18567,11 +18567,11 @@
         <v>1</v>
       </c>
       <c r="G525" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="G526" t="n">
-        <v>0</v>
+        <v>9414</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18805,11 +18805,11 @@
         <v>1</v>
       </c>
       <c r="G532" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18839,11 +18839,11 @@
         <v>1</v>
       </c>
       <c r="G533" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18873,11 +18873,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18941,11 +18941,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="n">
-        <v>968</v>
+        <v>0</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18975,11 +18975,11 @@
         <v>1</v>
       </c>
       <c r="G537" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19043,11 +19043,11 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19689,11 +19689,11 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19723,11 +19723,11 @@
         <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19757,11 +19757,11 @@
         <v>1</v>
       </c>
       <c r="G560" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19791,11 +19791,11 @@
         <v>1</v>
       </c>
       <c r="G561" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19995,11 +19995,11 @@
         <v>1</v>
       </c>
       <c r="G567" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="G568" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20063,11 +20063,11 @@
         <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20097,11 +20097,11 @@
         <v>1</v>
       </c>
       <c r="G570" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20165,11 +20165,11 @@
         <v>1</v>
       </c>
       <c r="G572" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20607,11 +20607,11 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20641,11 @@
         <v>1</v>
       </c>
       <c r="G586" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20675,11 +20675,11 @@
         <v>1</v>
       </c>
       <c r="G587" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20709,11 +20709,11 @@
         <v>1</v>
       </c>
       <c r="G588" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20743,11 +20743,11 @@
         <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0</v>
+        <v>23116</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20777,11 +20777,11 @@
         <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20811,11 +20811,11 @@
         <v>1</v>
       </c>
       <c r="G591" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21083,11 +21083,11 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>734</v>
+        <v>0</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21117,11 +21117,11 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21219,7 +21219,7 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21831,11 +21831,11 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21899,11 +21899,11 @@
         <v>1</v>
       </c>
       <c r="G623" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21933,11 +21933,11 @@
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -22035,11 +22035,11 @@
         <v>1</v>
       </c>
       <c r="G627" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22103,11 +22103,11 @@
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22137,11 +22137,11 @@
         <v>1</v>
       </c>
       <c r="G630" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22171,11 +22171,11 @@
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22205,11 +22205,11 @@
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22239,11 +22239,11 @@
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22273,11 +22273,11 @@
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>29593</v>
+        <v>0</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22307,11 +22307,11 @@
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>536</v>
+        <v>0</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         <v>1</v>
       </c>
       <c r="G637" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22443,7 +22443,7 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
@@ -23089,11 +23089,11 @@
         <v>1</v>
       </c>
       <c r="G658" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23123,11 +23123,11 @@
         <v>1</v>
       </c>
       <c r="G659" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23157,11 +23157,11 @@
         <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23191,11 +23191,11 @@
         <v>1</v>
       </c>
       <c r="G661" t="n">
-        <v>0</v>
+        <v>11063</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
@@ -24279,11 +24279,11 @@
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24313,11 +24313,11 @@
         <v>1</v>
       </c>
       <c r="G694" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24347,11 +24347,11 @@
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24381,11 +24381,11 @@
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24449,11 +24449,11 @@
         <v>1</v>
       </c>
       <c r="G698" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24483,11 +24483,11 @@
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
@@ -25231,11 +25231,11 @@
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25265,11 +25265,11 @@
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25299,11 +25299,11 @@
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25333,11 +25333,11 @@
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>21955</v>
+        <v>0</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25367,11 +25367,11 @@
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25401,11 +25401,11 @@
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25503,11 +25503,11 @@
         <v>1</v>
       </c>
       <c r="G729" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25537,11 +25537,11 @@
         <v>1</v>
       </c>
       <c r="G730" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25571,11 +25571,11 @@
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25605,11 +25605,11 @@
         <v>1</v>
       </c>
       <c r="G732" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25673,11 +25673,11 @@
         <v>1</v>
       </c>
       <c r="G734" t="n">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25707,11 +25707,11 @@
         <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25809,7 +25809,7 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26115,11 +26115,11 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -26421,11 +26421,11 @@
         <v>1</v>
       </c>
       <c r="G756" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26455,11 +26455,11 @@
         <v>1</v>
       </c>
       <c r="G757" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26489,11 +26489,11 @@
         <v>1</v>
       </c>
       <c r="G758" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26523,11 +26523,11 @@
         <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26591,11 +26591,11 @@
         <v>1</v>
       </c>
       <c r="G761" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26625,11 +26625,11 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26693,11 @@
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26727,7 +26727,7 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28325,11 +28325,11 @@
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28359,11 +28359,11 @@
         <v>1</v>
       </c>
       <c r="G813" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28393,11 +28393,11 @@
         <v>1</v>
       </c>
       <c r="G814" t="n">
-        <v>24933</v>
+        <v>0</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28427,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="G816" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28495,11 +28495,11 @@
         <v>1</v>
       </c>
       <c r="G817" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28563,11 +28563,11 @@
         <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28597,11 +28597,11 @@
         <v>1</v>
       </c>
       <c r="G820" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28631,11 +28631,11 @@
         <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28665,11 +28665,11 @@
         <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28869,11 +28869,11 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28903,11 +28903,11 @@
         <v>1</v>
       </c>
       <c r="G829" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28937,11 +28937,11 @@
         <v>1</v>
       </c>
       <c r="G830" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -28971,11 +28971,11 @@
         <v>1</v>
       </c>
       <c r="G831" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29039,11 +29039,11 @@
         <v>1</v>
       </c>
       <c r="G833" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29073,11 +29073,11 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -29175,7 +29175,7 @@
         <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
@@ -29243,11 +29243,11 @@
         <v>1</v>
       </c>
       <c r="G839" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29277,11 +29277,11 @@
         <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29345,11 +29345,11 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29379,11 +29379,11 @@
         <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29481,11 +29481,11 @@
         <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29515,11 +29515,11 @@
         <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29549,11 +29549,11 @@
         <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29651,11 +29651,11 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29753,11 +29753,11 @@
         <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -30161,11 +30161,11 @@
         <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30195,11 +30195,11 @@
         <v>1</v>
       </c>
       <c r="G867" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -30705,7 +30705,7 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
@@ -31181,11 +31181,11 @@
         <v>1</v>
       </c>
       <c r="G896" t="n">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31215,11 +31215,11 @@
         <v>1</v>
       </c>
       <c r="G897" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31283,11 +31283,11 @@
         <v>1</v>
       </c>
       <c r="G899" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31317,11 +31317,11 @@
         <v>1</v>
       </c>
       <c r="G900" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31351,11 +31351,11 @@
         <v>1</v>
       </c>
       <c r="G901" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31385,11 +31385,11 @@
         <v>1</v>
       </c>
       <c r="G902" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31623,11 +31623,11 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31657,11 +31657,11 @@
         <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31691,11 +31691,11 @@
         <v>1</v>
       </c>
       <c r="G911" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31725,11 +31725,11 @@
         <v>1</v>
       </c>
       <c r="G912" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31793,11 +31793,11 @@
         <v>1</v>
       </c>
       <c r="G914" t="n">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31827,11 +31827,11 @@
         <v>1</v>
       </c>
       <c r="G915" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -31929,7 +31929,7 @@
         <v>1</v>
       </c>
       <c r="G918" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H918" t="inlineStr">
         <is>
@@ -32235,11 +32235,11 @@
         <v>1</v>
       </c>
       <c r="G927" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32269,11 +32269,11 @@
         <v>1</v>
       </c>
       <c r="G928" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32303,11 +32303,11 @@
         <v>1</v>
       </c>
       <c r="G929" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H929" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32337,11 +32337,11 @@
         <v>1</v>
       </c>
       <c r="G930" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32405,11 +32405,11 @@
         <v>1</v>
       </c>
       <c r="G932" t="n">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="H932" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32439,11 +32439,11 @@
         <v>1</v>
       </c>
       <c r="G933" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H933" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32541,7 +32541,7 @@
         <v>1</v>
       </c>
       <c r="G936" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H936" t="inlineStr">
         <is>
@@ -32578,6 +32578,312 @@
         <v>19</v>
       </c>
       <c r="H937" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B938" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C938" t="n">
+        <v>11392</v>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F938" t="b">
+        <v>1</v>
+      </c>
+      <c r="G938" t="n">
+        <v>77</v>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>race_control</t>
+        </is>
+      </c>
+      <c r="B939" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C939" t="n">
+        <v>11392</v>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F939" t="b">
+        <v>1</v>
+      </c>
+      <c r="G939" t="n">
+        <v>39</v>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B940" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C940" t="n">
+        <v>11392</v>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F940" t="b">
+        <v>1</v>
+      </c>
+      <c r="G940" t="n">
+        <v>0</v>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="B941" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C941" t="n">
+        <v>11392</v>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F941" t="b">
+        <v>1</v>
+      </c>
+      <c r="G941" t="n">
+        <v>966</v>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C942" t="n">
+        <v>11392</v>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F942" t="b">
+        <v>1</v>
+      </c>
+      <c r="G942" t="n">
+        <v>90</v>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>pit</t>
+        </is>
+      </c>
+      <c r="B943" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C943" t="n">
+        <v>11392</v>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F943" t="b">
+        <v>0</v>
+      </c>
+      <c r="G943" t="n">
+        <v>0</v>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>skipped_not_applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>starting_grid</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C944" t="n">
+        <v>11392</v>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F944" t="b">
+        <v>1</v>
+      </c>
+      <c r="G944" t="n">
+        <v>0</v>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>zero_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>drivers</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C945" t="n">
+        <v>11392</v>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F945" t="b">
+        <v>1</v>
+      </c>
+      <c r="G945" t="n">
+        <v>22</v>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>team_radio</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C946" t="n">
+        <v>11392</v>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="F946" t="b">
+        <v>1</v>
+      </c>
+      <c r="G946" t="n">
+        <v>18</v>
+      </c>
+      <c r="H946" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -32641,11 +32947,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8004</v>
+        <v>8406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>698dda7d5a8c7cf82cc603678b2976d34726bc25b13ec3d97d0eb64b4e792716</t>
+          <t>6379dd4b2ddf6cfe719ffb1cd3df3e13a3ec5a4ba02b80c2c8a4462c96017915</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -32671,11 +32977,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5077</v>
+        <v>6135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>89f9fca578069657346a871f0703611099bcbe189d7720b308936cb8ab21a321</t>
+          <t>81575fe2930394a154ff71c4b9092c043234a74ed7e31b6672a765e80b6d2d20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -32701,11 +33007,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>246390</v>
+        <v>288134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60d4d3e3d8fa65972b2c90a402a9f7521346d94527537b94f2c5c66cd4000ecf</t>
+          <t>70b29d8d0335af8d5c9ab83359bdff85276dd29dddb3dd29d6a2aed163fb1d69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -32731,11 +33037,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31068</v>
+        <v>36495</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>b060a5e88c1347dc8d720a48deb88955251962ac46a34f5a232041c965ec40c9</t>
+          <t>3c84d0281675ecd1da2f6de9ca18257ec051870520c3c289df023a4b0eabf1d1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -32761,11 +33067,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4204</v>
+        <v>4797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>72916118b6d7844213d40fe9c5159c47ac7d2b5ceb559e80d15da73f9ad7bde6</t>
+          <t>b581391a9bc240a654c64740e05ed28a18f1da3bce79f7bfdbbf43d4446107de</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -32795,7 +33101,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>c8dde9e7ab52dd9cea0785b7dde592a80335503d5870274d86aaec05ddd19511</t>
+          <t>f7e91482896521b02b9f3b2500ca43c38bd6037faa9e16e5f00b990a7a03b6a6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -32821,11 +33127,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>c0024d58d99ff331d39885c2fb45fac81ab8cf51264c4a24a8da748f87b42fa6</t>
+          <t>1d76e862171e94343051ca99e234e06abd906d4ea89cfae54b517b1a286c2899</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32851,11 +33157,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1151</v>
+        <v>1306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16057aa7c72c838ab97d3a7b6a930bfb6fd9760acf80e19bf8d1019c3580fff8</t>
+          <t>56e91d819f898120dc2cff219de782b1260c400ad1e722ccc194f8fd12a8832c</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -32881,11 +33187,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>658</v>
+        <v>739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3cafb75cee0a32fcd14ef22a14206a8e0de35926d841582469aba803c807d171</t>
+          <t>ad9655a48b9ee5707d43042482e4c4da4369547ed2045077ba14c7c05ee64471</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -32910,7 +33216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P105"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40067,6 +40373,74 @@
         <v>1</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>11392</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1297</v>
+      </c>
+      <c r="G106" t="n">
+        <v>9</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>19</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>-05:00:00</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O106" t="b">
+        <v>0</v>
+      </c>
+      <c r="P106" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8406</v>
+        <v>6111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6135</v>
+        <v>2964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>288134</v>
+        <v>190141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36495</v>
+        <v>20643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4797</v>
+        <v>3293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>597</v>
+        <v>400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1306</v>
+        <v>833</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>739</v>
+        <v>400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,11 +1839,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3641,11 +3641,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3743,11 +3743,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3777,11 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>22276</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4797,11 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4831,11 +4831,11 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5681,11 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5715,11 +5715,11 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6089,11 +6089,11 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6123,11 +6123,11 @@
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6395,11 +6395,11 @@
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6599,11 +6599,11 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6701,11 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6735,11 +6735,11 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>28324</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -7755,11 +7755,11 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -9897,11 +9897,11 @@
         <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10373,11 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         <v>1</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
         <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10679,11 +10679,11 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
         <v>1</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10747,11 +10747,11 @@
         <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -10781,11 +10781,11 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11495,11 @@
         <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11529,11 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11563,11 +11563,11 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>25483</v>
+        <v>0</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11597,11 +11597,11 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11631,11 +11631,11 @@
         <v>1</v>
       </c>
       <c r="G321" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11733,11 +11733,11 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11801,11 +11801,11 @@
         <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -11835,11 +11835,11 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13977,11 +13977,11 @@
         <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15099,11 +15099,11 @@
         <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15133,11 +15133,11 @@
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15167,11 +15167,11 @@
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15201,11 +15201,11 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -15405,11 +15405,11 @@
         <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15439,11 +15439,11 @@
         <v>1</v>
       </c>
       <c r="G433" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15473,11 +15473,11 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15507,11 +15507,11 @@
         <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15575,11 +15575,11 @@
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         <v>1</v>
       </c>
       <c r="G438" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15711,11 +15711,11 @@
         <v>1</v>
       </c>
       <c r="G441" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15745,11 +15745,11 @@
         <v>1</v>
       </c>
       <c r="G442" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15779,11 +15779,11 @@
         <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15813,11 +15813,11 @@
         <v>1</v>
       </c>
       <c r="G444" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15881,11 @@
         <v>1</v>
       </c>
       <c r="G446" t="n">
-        <v>1116</v>
+        <v>0</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15915,11 +15915,11 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -15983,11 +15983,11 @@
         <v>1</v>
       </c>
       <c r="G449" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
         <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
@@ -16221,11 +16221,11 @@
         <v>1</v>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16255,11 +16255,11 @@
         <v>1</v>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16323,11 +16323,11 @@
         <v>1</v>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16357,11 @@
         <v>1</v>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16391,11 +16391,11 @@
         <v>1</v>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16425,11 +16425,11 @@
         <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16493,11 +16493,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16527,11 +16527,11 @@
         <v>1</v>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -16629,11 +16629,11 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16663,11 +16663,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16697,11 +16697,11 @@
         <v>1</v>
       </c>
       <c r="G470" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16731,11 +16731,11 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16799,11 @@
         <v>1</v>
       </c>
       <c r="G473" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16833,11 +16833,11 @@
         <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -16935,11 +16935,11 @@
         <v>1</v>
       </c>
       <c r="G477" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17037,11 +17037,11 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17105,11 +17105,11 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17139,11 +17139,11 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17241,7 +17241,7 @@
         <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
@@ -17411,11 +17411,11 @@
         <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17445,11 +17445,11 @@
         <v>1</v>
       </c>
       <c r="G492" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17513,11 +17513,11 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17547,11 +17547,11 @@
         <v>1</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17581,11 +17581,11 @@
         <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17615,11 +17615,11 @@
         <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -17853,11 +17853,11 @@
         <v>1</v>
       </c>
       <c r="G504" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17887,11 +17887,11 @@
         <v>1</v>
       </c>
       <c r="G505" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17921,11 +17921,11 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -17955,11 +17955,11 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18023,11 +18023,11 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="G510" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18159,11 +18159,11 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18193,11 +18193,11 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18227,11 +18227,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18261,11 +18261,11 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18329,11 +18329,11 @@
         <v>1</v>
       </c>
       <c r="G518" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18363,11 +18363,11 @@
         <v>1</v>
       </c>
       <c r="G519" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18397,11 +18397,11 @@
         <v>1</v>
       </c>
       <c r="G520" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18431,11 +18431,11 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -18465,7 +18465,7 @@
         <v>1</v>
       </c>
       <c r="G522" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
@@ -18635,11 +18635,11 @@
         <v>1</v>
       </c>
       <c r="G527" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18669,11 +18669,11 @@
         <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18703,11 +18703,11 @@
         <v>1</v>
       </c>
       <c r="G529" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -18771,11 +18771,11 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19077,11 +19077,11 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19111,11 +19111,11 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19145,11 +19145,11 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19179,11 +19179,11 @@
         <v>1</v>
       </c>
       <c r="G543" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19213,11 +19213,11 @@
         <v>1</v>
       </c>
       <c r="G544" t="n">
-        <v>28253</v>
+        <v>0</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19247,11 +19247,11 @@
         <v>1</v>
       </c>
       <c r="G545" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19281,11 +19281,11 @@
         <v>1</v>
       </c>
       <c r="G546" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19315,11 +19315,11 @@
         <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19383,11 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19417,11 +19417,11 @@
         <v>1</v>
       </c>
       <c r="G550" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19451,11 +19451,11 @@
         <v>1</v>
       </c>
       <c r="G551" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19485,11 +19485,11 @@
         <v>1</v>
       </c>
       <c r="G552" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19553,11 +19553,11 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19587,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -19689,7 +19689,7 @@
         <v>1</v>
       </c>
       <c r="G558" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
@@ -19859,11 +19859,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -19893,11 +19893,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20301,11 +20301,11 @@
         <v>1</v>
       </c>
       <c r="G576" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20369,11 +20369,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20403,11 +20403,11 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20471,11 +20471,11 @@
         <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20505,11 +20505,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20573,11 +20573,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
         <v>1</v>
       </c>
       <c r="G585" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
@@ -20845,11 +20845,11 @@
         <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20913,11 +20913,11 @@
         <v>1</v>
       </c>
       <c r="G594" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20947,11 @@
         <v>1</v>
       </c>
       <c r="G595" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -20981,11 +20981,11 @@
         <v>1</v>
       </c>
       <c r="G596" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21015,11 +21015,11 @@
         <v>1</v>
       </c>
       <c r="G597" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -21219,11 +21219,11 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21253,11 +21253,11 @@
         <v>1</v>
       </c>
       <c r="G604" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21287,11 +21287,11 @@
         <v>1</v>
       </c>
       <c r="G605" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21321,11 +21321,11 @@
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21389,11 +21389,11 @@
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21423,11 +21423,11 @@
         <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21525,11 +21525,11 @@
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21559,11 +21559,11 @@
         <v>1</v>
       </c>
       <c r="G613" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21593,11 +21593,11 @@
         <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21627,11 +21627,11 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21695,11 +21695,11 @@
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21729,11 +21729,11 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
@@ -22443,11 +22443,11 @@
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22477,11 +22477,11 @@
         <v>1</v>
       </c>
       <c r="G640" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22511,11 +22511,11 @@
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22545,11 @@
         <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22613,11 @@
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22647,11 +22647,11 @@
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -22749,7 +22749,7 @@
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
@@ -23667,11 +23667,11 @@
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23701,11 +23701,11 @@
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23735,11 @@
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23769,11 +23769,11 @@
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23803,11 +23803,11 @@
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>30616</v>
+        <v>0</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23837,11 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23871,11 +23871,11 @@
         <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -23973,7 +23973,7 @@
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
@@ -24585,11 +24585,11 @@
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24619,11 @@
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24653,11 +24653,11 @@
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24687,11 +24687,11 @@
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24755,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>617</v>
+        <v>0</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
@@ -25231,11 +25231,11 @@
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -25809,11 +25809,11 @@
         <v>1</v>
       </c>
       <c r="G738" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25843,11 +25843,11 @@
         <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25877,11 +25877,11 @@
         <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25911,11 +25911,11 @@
         <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -25979,11 +25979,11 @@
         <v>1</v>
       </c>
       <c r="G743" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26115,7 +26115,7 @@
         <v>1</v>
       </c>
       <c r="G747" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
@@ -26149,11 +26149,11 @@
         <v>1</v>
       </c>
       <c r="G748" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26183,11 +26183,11 @@
         <v>1</v>
       </c>
       <c r="G749" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26217,11 +26217,11 @@
         <v>1</v>
       </c>
       <c r="G750" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26727,11 +26727,11 @@
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26761,11 @@
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26795,11 +26795,11 @@
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26829,11 +26829,11 @@
         <v>1</v>
       </c>
       <c r="G768" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26863,11 +26863,11 @@
         <v>1</v>
       </c>
       <c r="G769" t="n">
-        <v>26935</v>
+        <v>0</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26897,11 +26897,11 @@
         <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26931,11 +26931,11 @@
         <v>1</v>
       </c>
       <c r="G771" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -26965,11 +26965,11 @@
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27033,7 +27033,7 @@
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
@@ -27067,11 +27067,11 @@
         <v>1</v>
       </c>
       <c r="G775" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27101,11 +27101,11 @@
         <v>1</v>
       </c>
       <c r="G776" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27135,11 +27135,11 @@
         <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27203,11 +27203,11 @@
         <v>1</v>
       </c>
       <c r="G779" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         <v>1</v>
       </c>
       <c r="G780" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27645,11 +27645,11 @@
         <v>1</v>
       </c>
       <c r="G792" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27679,11 +27679,11 @@
         <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27713,11 +27713,11 @@
         <v>1</v>
       </c>
       <c r="G794" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27747,11 +27747,11 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27815,11 +27815,11 @@
         <v>1</v>
       </c>
       <c r="G797" t="n">
-        <v>811</v>
+        <v>0</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27849,11 +27849,11 @@
         <v>1</v>
       </c>
       <c r="G798" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
@@ -28121,11 +28121,11 @@
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>1301</v>
+        <v>0</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28155,11 +28155,11 @@
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28223,11 +28223,11 @@
         <v>1</v>
       </c>
       <c r="G809" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28257,11 +28257,11 @@
         <v>1</v>
       </c>
       <c r="G810" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
         <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -29039,11 +29039,11 @@
         <v>1</v>
       </c>
       <c r="G833" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29073,11 +29073,11 @@
         <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29175,11 +29175,11 @@
         <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29209,11 +29209,11 @@
         <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29787,7 @@
         <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -29821,11 +29821,11 @@
         <v>1</v>
       </c>
       <c r="G856" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29855,11 +29855,11 @@
         <v>1</v>
       </c>
       <c r="G857" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29889,11 +29889,11 @@
         <v>1</v>
       </c>
       <c r="G858" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29923,11 +29923,11 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>21448</v>
+        <v>0</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29957,11 +29957,11 @@
         <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -29991,11 +29991,11 @@
         <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30025,11 +30025,11 @@
         <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30093,11 +30093,11 @@
         <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30127,11 +30127,11 @@
         <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30161,11 +30161,11 @@
         <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30195,11 +30195,11 @@
         <v>1</v>
       </c>
       <c r="G867" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30705,7 +30705,7 @@
         <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
@@ -30739,11 +30739,11 @@
         <v>1</v>
       </c>
       <c r="G883" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30773,11 +30773,11 @@
         <v>1</v>
       </c>
       <c r="G884" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30807,11 +30807,11 @@
         <v>1</v>
       </c>
       <c r="G885" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30841,11 +30841,11 @@
         <v>1</v>
       </c>
       <c r="G886" t="n">
-        <v>6839</v>
+        <v>0</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30875,11 +30875,11 @@
         <v>1</v>
       </c>
       <c r="G887" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30909,11 +30909,11 @@
         <v>1</v>
       </c>
       <c r="G888" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -30943,11 +30943,11 @@
         <v>1</v>
       </c>
       <c r="G889" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31011,11 +31011,11 @@
         <v>1</v>
       </c>
       <c r="G891" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31045,11 +31045,11 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31079,11 +31079,11 @@
         <v>1</v>
       </c>
       <c r="G893" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31113,11 +31113,11 @@
         <v>1</v>
       </c>
       <c r="G894" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31623,7 +31623,7 @@
         <v>1</v>
       </c>
       <c r="G909" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
@@ -31691,11 +31691,11 @@
         <v>1</v>
       </c>
       <c r="G911" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31725,11 +31725,11 @@
         <v>1</v>
       </c>
       <c r="G912" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31793,11 +31793,11 @@
         <v>1</v>
       </c>
       <c r="G914" t="n">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31827,11 +31827,11 @@
         <v>1</v>
       </c>
       <c r="G915" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31929,11 +31929,11 @@
         <v>1</v>
       </c>
       <c r="G918" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31963,11 +31963,11 @@
         <v>1</v>
       </c>
       <c r="G919" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -31997,11 +31997,11 @@
         <v>1</v>
       </c>
       <c r="G920" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32031,11 +32031,11 @@
         <v>1</v>
       </c>
       <c r="G921" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32099,11 +32099,11 @@
         <v>1</v>
       </c>
       <c r="G923" t="n">
-        <v>701</v>
+        <v>0</v>
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32133,11 +32133,11 @@
         <v>1</v>
       </c>
       <c r="G924" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32541,7 +32541,7 @@
         <v>1</v>
       </c>
       <c r="G936" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H936" t="inlineStr">
         <is>
@@ -32643,11 +32643,11 @@
         <v>1</v>
       </c>
       <c r="G939" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32711,11 +32711,11 @@
         <v>1</v>
       </c>
       <c r="G941" t="n">
-        <v>966</v>
+        <v>0</v>
       </c>
       <c r="H941" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32745,11 +32745,11 @@
         <v>1</v>
       </c>
       <c r="G942" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H942" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32847,11 +32847,11 @@
         <v>1</v>
       </c>
       <c r="G945" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32881,11 +32881,11 @@
         <v>1</v>
       </c>
       <c r="G946" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -32947,11 +32947,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8406</v>
+        <v>6111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6379dd4b2ddf6cfe719ffb1cd3df3e13a3ec5a4ba02b80c2c8a4462c96017915</t>
+          <t>1d86dfbcdc0130e6185e3c6213d5c5252b2f2ec7e623304119c6e8bb1b88fb92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -32977,11 +32977,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6135</v>
+        <v>2964</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>81575fe2930394a154ff71c4b9092c043234a74ed7e31b6672a765e80b6d2d20</t>
+          <t>23b98816d7d1c4cd9a5863e9c1f9481eaf41df9ec14c42c5af18c557d05633b3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -33007,11 +33007,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>288134</v>
+        <v>190141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>70b29d8d0335af8d5c9ab83359bdff85276dd29dddb3dd29d6a2aed163fb1d69</t>
+          <t>5a749975afa7dc85a4e5bb0ae9e078a3f8e529530d2435f63ef32a9cfdf96eab</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -33037,11 +33037,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36495</v>
+        <v>20643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3c84d0281675ecd1da2f6de9ca18257ec051870520c3c289df023a4b0eabf1d1</t>
+          <t>2d52ecaed4c20f50f50139a5ad8e37f99709af6e1d1d4e9cb146f4efeaef0784</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -33067,11 +33067,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4797</v>
+        <v>3293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>b581391a9bc240a654c64740e05ed28a18f1da3bce79f7bfdbbf43d4446107de</t>
+          <t>2e471161e23702e9f73819aec92dee13c0fc59efc5d7f5307692a010818a189a</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -33097,11 +33097,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>597</v>
+        <v>400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>f7e91482896521b02b9f3b2500ca43c38bd6037faa9e16e5f00b990a7a03b6a6</t>
+          <t>db2928b8f1c9baf55c84e896f06d32ce678e37a4edc0ae11459bd53b6f41d13d</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -33127,11 +33127,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1d76e862171e94343051ca99e234e06abd906d4ea89cfae54b517b1a286c2899</t>
+          <t>4650e2d9c5fd48d75471ccf0c96eecdac4ed5793d57219801f9b2395db1abdb6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -33157,11 +33157,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1306</v>
+        <v>833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56e91d819f898120dc2cff219de782b1260c400ad1e722ccc194f8fd12a8832c</t>
+          <t>7eb60c88eebdabc7797f29afc80bc1ae5147d2726204c412de47138646c4a36f</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -33187,11 +33187,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>739</v>
+        <v>400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ad9655a48b9ee5707d43042482e4c4da4369547ed2045077ba14c7c05ee64471</t>
+          <t>beb88230dfa6b97f4485ba73f86b04969680f953c8bd6759ada7dc4aa1661ea3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
+++ b/latest/openf1_lightweight_source_closure/F1_OpenF1_Lightweight_Source_Closure_Summary.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6111</v>
+        <v>5869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2964</v>
+        <v>3638</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>190141</v>
+        <v>175910</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20643</v>
+        <v>25693</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3293</v>
+        <v>3642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>833</v>
+        <v>995</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>492</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,11 +1839,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -1941,11 +1941,11 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2145,11 +2145,11 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2587,11 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2859,11 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -2961,11 +2961,11 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3029,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3199,11 +3199,11 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3233,11 +3233,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3267,11 +3267,11 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3335,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3369,11 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3539,11 +3539,11 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3573,11 +3573,11 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -3947,11 +3947,11 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -3981,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4083,11 +4083,11 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4151,11 +4151,11 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4253,11 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4457,11 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4491,11 +4491,11 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5001,11 @@
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5069,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5103,11 +5103,11 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5171,11 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5205,11 +5205,11 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5273,11 +5273,11 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5375,11 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5443,11 +5443,11 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>20663</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5477,11 +5477,11 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5511,11 +5511,11 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5545,11 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -5987,11 +5987,11 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6021,11 +6021,11 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -6837,11 +6837,11 @@
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6939,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>28324</v>
+        <v>0</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7041,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8061,11 +8061,11 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -8979,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -12345,11 +12345,11 @@
         <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12413,11 +12413,11 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>9131</v>
+        <v>0</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -13195,11 +13195,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13263,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13297,11 +13297,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13331,11 +13331,11 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13365,11 +13365,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13433,11 +13433,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13467,11 +13467,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -13569,11 +13569,11 @@
         <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>zero_rows</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -14181,11 +14181,11 @@
         <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14215,11 +14215,11 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>zero_rows</t>
         </is>
       </c>
     </row>
@@ -14249,11 +14249,11 @@
         <v>1</v>
       </c>
     